--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL/BN/BN_SILSILA SAHIHA.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL/BN/BN_SILSILA SAHIHA.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,1257 +433,1264 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>book_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>language_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>hadith_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>content</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>{"id":"1","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | ইসলামী ভ্রাতৃত্বের সুন্দর শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. সাহাবীদের মাঝে ভ্রাতৃত্বের বন্ধন গড়ে দেওয়ার মাধ্যমে ইসলামী সম্পর্কের গভীর শিক্ষা এখানে এসেছে।"},"content":{"heading":"ইসলামী ভ্রাতৃত্ব: সাহাবীদের বন্ধনের সুন্দর শিক্ষা","explanation":"এই হাদিসে দেখা যায়, রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম যুবায়ের রাঃ ও আব্দুল্লাহ ইবনু মাসউদ রাঃ-এর মধ্যে ভ্রাতৃত্বের বন্ধন রচনা করে দেন। এখানে ইসলামী ভ্রাতৃত্বের একটি সহজ কিন্তু গভীর শিক্ষা আছে। একজন মুসলিম শুধু নিজের পরিবার বা গোত্রের মানুষকেই আপন ভাবে না; ঈমানের সম্পর্কও তাকে অন্য মুসলিমের সঙ্গে কাছে নিয়ে আসে। এই বর্ণনায় কোনো বড় বক্তৃতা নেই, কিন্তু কাজটি নিজেই বড় শিক্ষা দেয়। মুসলিম সমাজে ভালো সম্পর্ক, পারস্পরিক সহায়তা এবং ভাইয়ের মতো আচরণ গুরুত্বপূর্ণ। হাদিসটি সহীহ বলা হয়েছে। তাই ভ্রাতৃত্বের বন্ধন, মুসলিম ভাইচারা এবং সাহাবীদের সম্পর্ক—এসব বিষয়ে এই হাদিসটি সুন্দর দিকনির্দেশনা দেয়।","teachings":["মুসলিমদের মধ্যে ভ্রাতৃত্বের বন্ধন গড়ে তোলা একটি সুন্দর ইসলামী শিক্ষা।","রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম সাহাবীদের মাঝে পারস্পরিক সম্পর্ক মজবুত করতেন।","ঈমানের সম্পর্ক মানুষকে একে অন্যের কাছে আপন করে তোলে।","ভালো সম্পর্ক সমাজে সহায়তা ও হৃদ্যতা বাড়াতে সাহায্য করে।"]},"searching_terms":["ইসলামী ভ্রাতৃত্ব হাদিস","সাহাবীদের ভ্রাতৃত্বের বন্ধন","যুবায়ের ও আব্দুল্লাহ ইবনু মাসউদ","মুসলিম ভাইচারা হাদিস","সিলসিলা সহিহা ১","ভ্রাতৃত্বের শিক্ষা ইসলাম"],"related_hadiths":["সিলসিলা সহিহা ১৬","সিলসিলা সহিহা ১৭","সিলসিলা সহিহা ৮ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>{"id":"10","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | ক্রোধ নিয়ন্ত্রণের সহজ উপদেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. কম কথা, গভীর শিক্ষা—রাসুল সাল্লাল্লাহু আলাইহি ওয়াসাল্লাম বারবার ক্রোধ নিয়ন্ত্রণ করতে বলেছেন।"},"content":{"heading":"ক্রোধ নিয়ন্ত্রণ কর: জীবনের জন্য ছোট কিন্তু বড় উপদেশ","explanation":"এই হাদিসে একজন ব্যক্তি রাসুলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামকে বলেন, আমাকে এমন কিছু বাক্য বলুন, যার অনুযায়ী আমি জীবনযাপন করতে পারি। তিনি আরও বলেন, বেশি বলবেন না, যেন আমি ভুলে না যাই। উত্তরে রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেন, ক্রোধ নিয়ন্ত্রণ কর। লোকটি আবার প্রশ্ন করলে তিনি আবারও বলেন, ক্রোধ নিয়ন্ত্রণ কর। হাদিসটি সহীহ বলা হয়েছে। এখানে ক্রোধ নিয়ন্ত্রণের শিক্ষা খুব স্পষ্ট। মানুষ রাগের সময় এমন কথা বা কাজ করে ফেলতে পারে, যা পরে কষ্টের কারণ হয়। তাই অল্প কথায় এই হাদিস জীবন বদলানোর মতো উপদেশ দেয়। রাগ সামলানো, কথা সংযত রাখা এবং নিজের আচরণ ঠিক রাখা—এসব এই শিক্ষার সঙ্গে যুক্ত।","teachings":["ক্রোধ নিয়ন্ত্রণ করা মুসলিম চরিত্রের গুরুত্বপূর্ণ অংশ।","জীবনের জন্য কখনো ছোট উপদেশও বড় কাজে আসে।","একই উপদেশ পুনরাবৃত্তি করে এর গুরুত্ব বোঝানো হয়েছে।","রাগের সময় কথা ও কাজ সামলানো দরকার।"]},"searching_terms":["ক্রোধ নিয়ন্ত্রণ কর হাদিস","রাগ নিয়ন্ত্রণের হাদিস","সিলসিলা সহিহা ১০","ইসলামে রাগ কমানোর উপদেশ","রাসুলের সংক্ষিপ্ত উপদেশ","রাগ সামলানোর ইসলামিক শিক্ষা"],"related_hadiths":["সিলসিলা সহিহা ৪","সিলসিলা সহিহা ১৪","সিলসিলা সহিহা ১১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>{"id":"11","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | প্রতিশোধ নয় ক্ষমার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. আবূ বকর রাঃ ও রাবিয়াহর ঘটনায় প্রতিশোধ না নিয়ে ক্ষমার দোয়া করার শিক্ষা এসেছে।"},"content":{"heading":"ক্ষমার দোয়া: আবূ বকর রাঃ ও রাবিয়াহর ঘটনার শিক্ষা","explanation":"এই দীর্ঘ হাদিসে রাবিয়াহ রাঃ ও আবূ বকর রাঃ-এর একটি ঘটনা এসেছে। জমির সীমানায় একটি ফলবান খেজুর গাছ নিয়ে তাঁদের মধ্যে মতভেদ হয়। কথাবার্তার সময় আবূ বকর রাঃ এমন কথা বলেন, যা রাবিয়াহ রাঃ অপছন্দ করেন। পরে আবূ বকর রাঃ লজ্জিত হন এবং রাবিয়াহকে বলেন, তিনিও যেন একই ধরনের কথা ফিরিয়ে দেন, যাতে বদলা হয়ে যায়। কিন্তু রাবিয়াহ তা করতে চাননি। শেষে বিষয়টি রাসুলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামের কাছে আসে। তিনি রাবিয়াহকে প্রতিশোধ নিতে বলেননি; বরং বলতে বলেন, হে আবূ বকর, আল্লাহ তোমাকে ক্ষমা করুন। হাদিসটি সহীহ বলা হয়েছে। এখানে ক্ষমা, রাগ নিয়ন্ত্রণ, বড়দের মর্যাদা এবং সম্পর্ক রক্ষার সুন্দর শিক্ষা আছে।","teachings":["ভুল কথা হয়ে গেলে লজ্জিত হওয়া ও সংশোধনের চেষ্টা করা ভালো।","প্রতিশোধ না নিয়ে ক্ষমার দোয়া করা উত্তম আচরণের অংশ।","সাহাবীরা মর্যাদাবান ব্যক্তির সম্মান রক্ষায় সতর্ক ছিলেন।","মতভেদ হলে রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামের নির্দেশ মেনে চলা উচিত।"]},"searching_terms":["আবু বকর রাবিয়াহ ঘটনা","প্রতিশোধ নয় ক্ষমা হাদিস","আল্লাহ তোমাকে ক্ষমা করুন হাদিস","সিলসিলা সহিহা ১১","ক্ষমার দোয়া হাদিস","সাহাবীদের ক্ষমার ঘটনা"],"related_hadiths":["সিলসিলা সহিহা ১০","সিলসিলা সহিহা ১৪","সিলসিলা সহিহা ৯ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>{"id":"13","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | আল্লাহর প্রিয় বান্দার চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর নিকট প্রিয় বান্দা কে—এর উত্তরে বেশি চরিত্রবান হওয়ার শিক্ষা এসেছে।"},"content":{"heading":"আল্লাহর প্রিয় বান্দা: উত্তম চরিত্রের বড় মর্যাদা","explanation":"এই হাদিসে বর্ণনাকারী বলেন, তারা নাবী কারীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামের কাছে খুব নীরবে বসে ছিলেন, যেন মাথার ওপর পাখি বসে আছে। এমন সময় কিছু মানুষ এসে জিজ্ঞেস করল, আল্লাহর নিকট কোন বান্দা সবচেয়ে প্রিয়? রাসুলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বললেন, যে সবচেয়ে বেশি চরিত্রবান, সে-ই আল্লাহর কাছে প্রিয়। হাদিসটি সহীহ বলা হয়েছে। এখানে উত্তম চরিত্রের গুরুত্ব খুব সুন্দরভাবে এসেছে। ভালো চরিত্র মানে শুধু হাসিমুখ নয়; কথা, ব্যবহার, রাগ, সম্পর্ক—সব জায়গায় এর ছাপ থাকে। আল্লাহর প্রিয় বান্দা হওয়ার আশা যারা করে, তাদের জন্য চরিত্র ঠিক করা বড় শিক্ষা। এই হাদিস উত্তম চরিত্র, ভালো ব্যবহার এবং নীরবভাবে শেখার আদবও মনে করিয়ে দেয়।","teachings":["আল্লাহর কাছে প্রিয় হওয়ার সাথে উত্তম চরিত্রের সম্পর্ক আছে।","সাহাবীরা নাবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামের সামনে খুব আদবের সাথে বসতেন।","ভালো চরিত্র মানুষের কথা ও আচরণে প্রকাশ পায়।","চরিত্র সুন্দর করা মুমিনের নিয়মিত কাজ হওয়া উচিত।"]},"searching_terms":["আল্লাহর প্রিয় বান্দা হাদিস","সবচেয়ে বেশি চরিত্রবান হাদিস","সিলসিলা সহিহা ১৩","উত্তম চরিত্রের ফজিলত","ভালো চরিত্রের হাদিস","আল্লাহর কাছে প্রিয় মানুষ"],"related_hadiths":["সিলসিলা সহিহা ৯","সিলসিলা সহিহা ১২","সিলসিলা সহিহা ৭ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>{"id":"14","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | জিহ্বা সংযমের কঠিন শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. জিহ্বা সংযত করার নির্দেশ এবং কথার কারণে মানুষের বিপদে পড়ার সতর্কতা এতে এসেছে।"},"content":{"heading":"জিহ্বা সংযম: কথার বিপদ থেকে বাঁচার হাদিস","explanation":"এই বর্ণনায় বলা হয়েছে, তোমরা জিহ্বা সংযত কর। এরপর মুয়াজ রাঃ-কে উদ্দেশ করে বলা হয়েছে, জিহ্বাই মানুষকে অধোমুখী করে। অর্থাৎ মানুষ অনেক সময় নিজের কথার কারণেই বিপদে পড়ে। হাদিসটি সহীহ বলা হয়েছে। এখানে জিহ্বা সংযমের শিক্ষা খুব সরাসরি। মানুষের মুখ থেকে বের হওয়া কথা সম্পর্ক গড়ে, আবার সম্পর্ক ভাঙতেও পারে। চোগলখুরী, ঝগড়া, রাগের কথা—এসবের মূলেও জিহ্বার ভুল ব্যবহার থাকতে পারে। তাই এই হাদিস কথা বলার আগে ভেবে নেওয়ার শিক্ষা দেয়। কথার কারণে ক্ষতি হতে পারে—এই সতর্কতা একজন মুসলিমকে নরম, সংযত এবং দায়িত্বশীল করে। জিহ্বা সংযম হাদিস দৈনন্দিন জীবনের জন্য খুব দরকারি শিক্ষা।","teachings":["জিহ্বা সংযত করা ইসলামী চরিত্রের গুরুত্বপূর্ণ অংশ।","কথার কারণে মানুষ বিপদে পড়তে পারে।","কথা বলার আগে ভাবা দরকার।","ঝগড়া, চোগলখুরী ও রাগের কথার দরজা বন্ধ করতে জিহ্বা সামলানো জরুরি।"]},"searching_terms":["জিহ্বা সংযম হাদিস","জিহ্বাই মানুষকে অধোমুখী করে","সিলসিলা সহিহা ১৪","কথা সংযম ইসলাম","মুখের কথা নিয়ে হাদিস","জিহ্বার ক্ষতি হাদিস"],"related_hadiths":["সিলসিলা সহিহা ৫","সিলসিলা সহিহা ৪","সিলসিলা সহিহা ১০ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>{"id":"15","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | খাদেমের সাথে সদাচরণের শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাবার আনা খাদেমের কষ্টকে মূল্য দিয়ে তাকে সাথে বসানো বা লোকমা দেওয়ার শিক্ষা এসেছে।"},"content":{"heading":"খাদেমের সাথে সদাচরণ: খাবারের সময় ন্যায্যতার সুন্দর শিক্ষা","explanation":"এই হাদিসে বলা হয়েছে, যখন কারো খাদেম খাবার নিয়ে আসে, সে খাবার প্রস্তুত করতে গিয়ে আগুনের তাপ ও কষ্ট সহ্য করেছে। তাই তাকে খাওয়ার জন্য সাথে বসাতে বলা হয়েছে। যদি সে খেতে না চায়, তবে তার হাতে এক লোকমা দিতে বলা হয়েছে। হাদিসটি সহীহ বলা হয়েছে। এখানে খাদেমের সাথে সদাচরণ ও কষ্টের মূল্য দেওয়ার শিক্ষা এসেছে। যে মানুষ খাবার তৈরি করে, সে শুধু কাজ করছে—এভাবে দেখা নয়; তার শ্রম, তাপ, ক্লান্তি এবং মানবিক অধিকারও ভাবতে হবে। এই হাদিস সমাজে দুর্বল বা কর্মরত মানুষের প্রতি সম্মান শেখায়। খাবারের সময় খাদেমকে ভুলে না যাওয়া, তাকে অংশ দেওয়া এবং ভালো আচরণ করা—এসবই উত্তম চরিত্রের অংশ।","teachings":["খাদেম বা কর্মচারীর কষ্টকে সম্মান করা উচিত।","খাবার আনলে তাকে সাথে বসানোর শিক্ষা এসেছে।","সে না খেতে চাইলে অন্তত এক লোকমা দেওয়ার কথা বলা হয়েছে।","মানুষের শ্রম ও কষ্টের মূল্য দেওয়া ভালো চরিত্রের অংশ।"]},"searching_terms":["খাদেমের সাথে সদাচরণ হাদিস","কর্মচারীকে খাবার দেওয়ার হাদিস","সিলসিলা সহিহা ১৫","খাদেম খাবার নিয়ে এলে হাদিস","ইসলামে কর্মচারীর অধিকার","খাবারের সময় খাদেমের অধিকার"],"related_hadiths":["সিলসিলা সহিহা ১৯","সিলসিলা সহিহা ৯","সিলসিলা সহিহা ১৭ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>{"id":"17","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | গৃহে হৃদ্যতা আল্লাহর দান","description":"$book_name$ $hadith_number$ - $chapter_name$. কোনো পরিবারের মঙ্গল চাইলে আল্লাহ তাদের মধ্যে হৃদ্যতা সৃষ্টি করেন—এই সুন্দর শিক্ষা এসেছে।"},"content":{"heading":"গৃহে হৃদ্যতা: পরিবারের মঙ্গলের সুন্দর চিহ্ন","explanation":"এই হাদিসে ‘আয়িশা রাঃ থেকে বর্ণিত হয়েছে, যখন আল্লাহ তায়ালা কোনো গৃহবাসীর মঙ্গল চান, তখন তাদের মধ্যে হৃদ্যতা সৃষ্টি করে দেন। হাদিসটি সহীহ বলা হয়েছে। এখানে পরিবারের ভেতরের ভালোবাসা, নরম আচরণ এবং একে অন্যের প্রতি মায়ার গুরুত্ব বোঝানো হয়েছে। একটি ঘরে শুধু খাবার, সম্পদ বা বাহ্যিক ব্যবস্থা থাকলেই শান্তি আসে না; হৃদ্যতা থাকাও বড় বিষয়। পরিবারের মানুষ যদি একে অন্যকে বুঝতে চায়, ভালো ব্যবহার করে এবং সম্পর্ক নষ্ট না করে, তাহলে ঘরে শান্তির পরিবেশ তৈরি হয়। এই হাদিস গৃহে হৃদ্যতা, পারিবারিক সম্পর্ক এবং আল্লাহর পক্ষ থেকে মঙ্গলের শিক্ষা দেয়। তাই পরিবারে ভালো কথা, ক্ষমা ও নরম আচরণ গুরুত্ব পাওয়া উচিত।","teachings":["পরিবারের মধ্যে হৃদ্যতা আল্লাহর মঙ্গলের একটি সুন্দর দান।","গৃহে ভালোবাসা ও নরম আচরণ গুরুত্বপূর্ণ।","সম্পর্ক ভালো থাকলে পরিবারে শান্তি বাড়তে পারে।","পরিবারের মানুষদের একে অন্যের প্রতি সদয় হওয়া উচিত।"]},"searching_terms":["গৃহে হৃদ্যতা হাদিস","পরিবারের মঙ্গল হাদিস","সিলসিলা সহিহা ১৭","পরিবারে ভালোবাসা ইসলাম","আল্লাহ মঙ্গল চাইলে হৃদ্যতা দেন","পারিবারিক সম্পর্ক হাদিস"],"related_hadiths":["সিলসিলা সহিহা ১৬","সিলসিলা সহিহা ১","সিলসিলা সহিহা ১৫ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>{"id":"18","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | স্বপ্নের প্রকার ও করণীয়","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিমের স্বপ্ন, সত্যবাদিতা, স্বপ্নের তিন ধরন এবং অপ্রীতিকর স্বপ্নে করণীয় শেখানো হয়েছে।"},"content":{"heading":"স্বপ্নের প্রকার: শুভ স্বপ্ন, শয়তানের স্বপ্ন ও করণীয়","explanation":"এই হাদিসে স্বপ্ন সম্পর্কে কয়েকটি শিক্ষা এসেছে। কিয়ামাত নিকটবর্তী হলে মুসলিমের স্বপ্ন মিথ্যা হবে না—এ কথা বলা হয়েছে। আরও বলা হয়েছে, মানুষের মধ্যে যে বেশি সত্যবাদী, সে বেশি সত্য স্বপ্ন দেখতে পাবে। মুসলিমের স্বপ্ন নবুওতের ছেচল্লিশ ভাগের এক ভাগ বলা হয়েছে। এরপর স্বপ্ন তিন প্রকার বলা হয়েছে। এক, শুভ স্বপ্ন, যা আল্লাহর পক্ষ থেকে সুসংবাদ। দুই, শাইত্বানের পক্ষ থেকে পেরেশানিমূলক স্বপ্ন। তিন, মানুষের নিজের চিন্তা বা কল্পনা থেকে আসা স্বপ্ন। কেউ অপ্রীতিকর স্বপ্ন দেখলে তা কারো কাছে না বলতে এবং দাঁড়িয়ে সালাত আদায় করতে বলা হয়েছে। হাদিসটি সহীহ। এখানে স্বপ্নের প্রকার, সত্যবাদিতা এবং অপছন্দের স্বপ্নে করণীয় পরিষ্কারভাবে এসেছে।","teachings":["স্বপ্ন তিন ধরনের হতে পারে—শুভ, শাইত্বানের পক্ষের, আর নিজের কল্পনা থেকে।","সত্যবাদী মানুষের সত্য স্বপ্ন দেখার কথা বর্ণনায় এসেছে।","অপ্রীতিকর স্বপ্ন দেখলে তা অন্যকে না বলতে বলা হয়েছে।","অপছন্দের স্বপ্নের পর সালাত আদায়ের নির্দেশ এসেছে।"]},"searching_terms":["স্বপ্ন তিন প্রকার হাদিস","মুসলিমের স্বপ্ন নবুওতের ছেচল্লিশ ভাগ","অপ্রীতিকর স্বপ্ন দেখলে করণীয়","সিলসিলা সহিহা ১৮","সত্য স্বপ্ন হাদিস","শুভ স্বপ্ন আল্লাহর পক্ষ থেকে"],"related_hadiths":["সিলসিলা সহিহা ৯ (প্রাসঙ্গিক বর্ণনা)","সিলসিলা সহিহা ১৩ (প্রাসঙ্গিক বর্ণনা)","সিলসিলা সহিহা ১৪ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>{"id":"19","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | সেবকের খাবারের অধিকার","description":"$book_name$ $hadith_number$ - $chapter_name$. সেবক খাবার আনলে তার কষ্টের মূল্য দিয়ে সাথে খাওয়ানো বা খাবার থেকে লোকমা দেওয়ার শিক্ষা এসেছে।"},"content":{"heading":"সেবকের অধিকার: খাবার আনার কষ্টকে সম্মান করার হাদিস","explanation":"এই হাদিসে আবু হুরাইরাহ রাঃ থেকে বর্ণিত হয়েছে, কারো খাদেম বা সেবক যখন খাবার নিয়ে আসে, সে আগুনের গরম ও কাজের কষ্ট সহ্য করেছে। যদি তাকে সঙ্গে বসিয়ে খাওয়ানো না হয়, তাহলে সেই খাবার থেকে অন্তত এক লোকমা হলেও তাকে দিতে বলা হয়েছে। হাদিসটি সহীহ। এই বর্ণনা সেবকের অধিকার ও মানবিক আচরণের শিক্ষা দেয়। যে মানুষ খাবার তৈরি করেছে, তার শ্রমকে অবহেলা করা উচিত নয়। ইসলাম মানুষকে শুধু নিজের আরাম দেখার শিক্ষা দেয় না; অন্যের কষ্টও ভাবতে শেখায়। খাদেমের সাথে সদাচরণ, কর্মচারীর প্রতি সম্মান এবং খাবারের সময় ন্যায্য ব্যবহার—এই হাদিসের মূল শিক্ষা। একই বিষয়ে আরেকটি বর্ণনার সাথেও এর মিল আছে।","teachings":["সেবকের শ্রম ও কষ্টের মূল্য দেওয়া উচিত।","খাবার প্রস্তুতকারী মানুষকে অবহেলা করা ঠিক নয়।","সাথে খাওয়ানো না হলে অন্তত খাবার থেকে কিছু দেওয়ার নির্দেশ এসেছে।","কর্মচারী বা সেবকের সাথে সদাচরণ উত্তম চরিত্রের অংশ।"]},"searching_terms":["সেবকের খাবারের অধিকার হাদিস","খাদেম খাবার আনলে হাদিস","সিলসিলা সহিহা ১৯","কর্মচারীর প্রতি সদাচরণ","খাবার থেকে এক লোকমা দেওয়া","ইসলামে সেবকের অধিকার"],"related_hadiths":["সিলসিলা সহিহা ১৫","সিলসিলা সহিহা ৯","সিলসিলা সহিহা ১৭ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>{"id":"2","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | লজ্জা-শরম ও নৈতিকতার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. লজ্জা-শরম না থাকলে মানুষ সীমা ছাড়িয়ে যেতে পারে—এই হাদিসে নৈতিক সতর্কতার শিক্ষা এসেছে।"},"content":{"heading":"লজ্জা-শরম: নৈতিক জীবনের গুরুত্বপূর্ণ শিক্ষা","explanation":"এই হাদিসে বলা হয়েছে, পূর্ববর্তী নাবুওয়াতের বাণী থেকে মানুষ যে শেষ শিক্ষাটি পেয়েছে, তা হলো—যখন তোমার লজ্জা-শরম নেই, তখন তুমি যা ইচ্ছা তাই কর। কথাটি শুনতে কঠিন মনে হতে পারে, কিন্তু এর ভেতরে বড় সতর্কতা আছে। লজ্জা-শরম মানুষের চরিত্রকে আটকায়, খারাপ কথা ও খারাপ কাজ থেকে দূরে রাখে। যখন মানুষের মনে লজ্জা থাকে না, তখন সে নিজের কাজের ফল নিয়েও কম ভাবতে পারে। তাই এই হাদিস লজ্জা-শরম, নৈতিকতা এবং চরিত্র গঠনের বিষয়ে গুরুত্বপূর্ণ শিক্ষা দেয়। হাদিসটি সহীহ বলা হয়েছে। মুসলিম জীবনে লজ্জা মানে দুর্বলতা নয়; বরং এটি খারাপ কাজ থেকে বাঁচার একটি সুন্দর গুণ।","teachings":["লজ্জা-শরম মানুষকে খারাপ কাজ থেকে বিরত রাখতে সাহায্য করে।","লজ্জা না থাকলে মানুষ নিজের সীমা ভুলে যেতে পারে।","নৈতিক জীবন গড়তে চরিত্রের ভেতরের সংযম দরকার।","পূর্ববর্তী নাবুওয়াতের শিক্ষাতেও লজ্জার গুরুত্ব ছিল।"]},"searching_terms":["লজ্জা শরম হাদিস","যখন লজ্জা নেই যা ইচ্ছা কর","সিলসিলা সহিহা ২","ইসলামে লজ্জার গুরুত্ব","লজ্জা ঈমানের অংশ হাদিস","নৈতিকতা ও লজ্জা ইসলাম"],"related_hadiths":["সিলসিলা সহিহা ১৪","সিলসিলা সহিহা ৯","সিলসিলা সহিহা ১৩ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>{"id":"20","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসলিম ভাইয়ের দিকে অস্ত্র তোলার সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিম ভাইকে হত্যার উদ্দেশ্যে তরবারী তোলা থেকে ফেরেশতাদের লানতের কঠিন সতর্কতা এসেছে।"},"content":{"heading":"মুসলিম ভাইয়ের দিকে অস্ত্র তোলা: কঠিন সতর্কতার হাদিস","explanation":"এই হাদিসে রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, যখন কোনো মুসলিম তার অপর মুসলিম ভাইয়ের উপর তাকে হত্যার উদ্দেশ্যে তরবারী তোলে, তখন ফেরেশতারা তার উপর লানত করতে থাকে, যতক্ষণ না সে তরবারী কোষাবদ্ধ করে। অর্থাৎ হত্যার ইচ্ছা ত্যাগ করে অস্ত্র খাপে না রাখা পর্যন্ত এই সতর্কতা থাকে। হাদিসটি হাসান বলা হয়েছে। এখানে মুসলিমের প্রাণ, নিরাপত্তা এবং ভাইয়ের প্রতি শত্রুতা না করার শিক্ষা এসেছে। রাগ, ঝগড়া বা শত্রুতার কারণে অস্ত্র তুলে নেওয়া খুব ভয়াবহ কাজ। এই হাদিস মুসলিম ভাইয়ের দিকে অস্ত্র তোলা, হত্যার ইচ্ছা এবং হিংসা থেকে দূরে থাকার বিষয়ে স্পষ্ট সতর্কতা দেয়। সম্পর্ক নষ্ট হলে সমাধান চাই, আক্রমণ নয়।","teachings":["মুসলিম ভাইয়ের বিরুদ্ধে হত্যার উদ্দেশ্যে অস্ত্র তোলা ভয়াবহ কাজ।","তরবারী খাপে না রাখা পর্যন্ত ফেরেশতাদের লানতের কথা এসেছে।","হত্যার ইচ্ছা ত্যাগ করা এবং অস্ত্র নামানো জরুরি।","রাগ বা শত্রুতার সময় নিজেকে থামানো দরকার।"]},"searching_terms":["মুসলিম ভাইয়ের দিকে অস্ত্র তোলা হাদিস","তরবারী উত্তোলন হাদিস","ফেরেশতাদের লানত হাদিস","সিলসিলা সহিহা ২০","মুসলিমকে হত্যা করার ইচ্ছা","ইসলামে ভাইয়ের নিরাপত্তা"],"related_hadiths":["সিলসিলা সহিহা ১০","সিলসিলা সহিহা ৪","সিলসিলা সহিহা ১৪ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>{"id":"22","core_topic":"ক্রোধ","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | রাগ কমানোর দোয়া ও শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. রাগের সময় আউযুবিল্লাহ বলার মাধ্যমে নিজেকে সংযত করা ও ক্রোধ প্রশমনের সুন্দর শিক্ষা।"},"content":{"heading":"রাগ কমানোর দোয়া: আউযুবিল্লাহ বলার শিক্ষা","explanation":"এই সহীহ হাদিসে রাগ নিয়ন্ত্রণের একটি সহজ আমল বলা হয়েছে। আবু হুরাইরাহ (রাঃ) থেকে বর্ণিত, কোনো ব্যক্তি ক্রুদ্ধ হলে সে যদি “আউযুবিল্লাহ” বলে, তাহলে তার ক্রোধ প্রশমিত হয়ে যাবে। এখানে মূল বিষয় হলো ক্রোধের সময় নিজের জিহ্বা ও আচরণকে নিয়ন্ত্রণ করা। রাগ মানুষের বিচারবুদ্ধি দুর্বল করে দিতে পারে। তাই রাগ উঠলে সঙ্গে সঙ্গে আল্লাহর কাছে আশ্রয় চাওয়া একটি সুন্দর শিক্ষা। “রাগ কমানোর দোয়া” বা “ক্রোধ নিয়ন্ত্রণের হাদিস” খুঁজলে এই ধরনের বর্ণনা মানুষকে বাস্তব জীবনে সাহায্য করে। হাদিসটি আমাদের শেখায়, রাগের মুহূর্তে তর্ক বাড়ানো নয়, বরং আল্লাহর স্মরণে ফিরে আসা ভালো পথ। এতে মানুষ নিজের কথা, কাজ ও সম্পর্ককে বেশি নিরাপদ রাখতে পারে।","teachings":["রাগ উঠলে আল্লাহর কাছে আশ্রয় চাওয়া উচিত।","ক্রোধের সময় দ্রুত জবাব না দিয়ে নিজেকে থামানো ভালো।","আউযুবিল্লাহ বলা রাগ কমানোর একটি সহজ আমল।","রাগ নিয়ন্ত্রণ করা উত্তম চরিত্রের অংশ।"]},"searching_terms":["রাগ কমানোর দোয়া","ক্রোধ নিয়ন্ত্রণের হাদিস","রাগ হলে আউযুবিল্লাহ বলা","রাগ কমানোর ইসলামিক উপায়","আউযুবিল্লাহ বলার ফজিলত","রাগ সম্পর্কে সহীহ হাদিস","রাগ প্রশমনের দোয়া"],"related_hadiths":["সহীহ বুখারী ৬১১৫","সহীহ মুসলিম ২৬১০","সুনান আবু দাউদ ৪৭৮১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>{"id":"23","core_topic":"মুসাফাহা","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | মুসাফাহার ফজিলত ও মুসলিম ভ্রাতৃত্ব","description":"$book_name$ $hadith_number$ - $chapter_name$. মুসলিম ভাইয়ের সঙ্গে সাক্ষাৎ ও মুসাফাহার মাধ্যমে গুনাহ ঝরে পড়া এবং হৃদ্যতা তৈরির শিক্ষা।"},"content":{"heading":"মুসাফাহার ফজিলত ও মুসলিম ভাইয়ের সঙ্গে হৃদ্যতা","explanation":"এই সহীহ হাদিসে মুসলিম ভাইয়ের সঙ্গে সাক্ষাৎ করে হাত ধরে মুসাফাহা করার ফজিলত বলা হয়েছে। বর্ণনায় এসেছে, দুই মুসলিম যখন দেখা করে এবং করমর্দন করে, তখন তাদের আঙুল থেকে গুনাহ ঝরে পড়ে, যেমন শীতকালে গাছের পাতা ঝরে। এরপর মুজাহিদ (রহ.) বিষয়টিকে হালকা করে না দেখার শিক্ষা দেন এবং সূরা আল-আনফালের ৬৩ নম্বর আয়াতের কথা উল্লেখ করেন, যেখানে হৃদয়ের বন্ধন আল্লাহর পক্ষ থেকে হওয়ার কথা এসেছে। তাই মুসাফাহা শুধু সামাজিক অভ্যাস নয়; এটি মুসলিম ভ্রাতৃত্ব, ভালোবাসা ও সম্পর্ক মজবুত করার একটি সুন্দর আমল। “মুসাফাহার ফজিলত” বা “করমর্দনের হাদিস” খুঁজলে এই হাদিসের মূল বার্তা হলো—ছোট মনে হওয়া ভালো কাজও আল্লাহর কাছে মূল্যবান হতে পারে।","teachings":["মুসলিম ভাইয়ের সঙ্গে দেখা হলে মুসাফাহা করা ভালো আমল।","আন্তরিক সম্পর্ক আল্লাহর দান, শুধু বাহ্যিক চেষ্টা নয়।","ছোট মনে হওয়া আমলকেও অবহেলা করা উচিত নয়।","মুসাফাহা মুসলিমদের মধ্যে ভালোবাসা বাড়াতে সাহায্য করে।"]},"searching_terms":["মুসাফাহার ফজিলত","করমর্দনের হাদিস","মুসলিম ভাইয়ের সাথে মুসাফাহা","মুসাফাহা করলে গুনাহ ঝরে","সাক্ষাতের আদব হাদিস","মুসলিম ভ্রাতৃত্বের হাদিস","হাত মেলানোর সুন্নত"],"related_hadiths":["সুনান আবু দাউদ ৫২১২","জামে আত-তিরমিজি ২৭২৭","সুনান ইবনু মাজাহ ৩৭০৩ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>{"id":"24","core_topic":"হাজ্জ","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | মৃত বাবার পক্ষ থেকে হাজ্জ করার বিধান","description":"$book_name$ $hadith_number$ - $chapter_name$. বাবা হাজ্জ না করে মারা গেলে সন্তানের পক্ষ থেকে তার হাজ্জ আদায়ের অনুমতি ও ঋণ পরিশোধের তুলনা।"},"content":{"heading":"মৃত বাবার পক্ষ থেকে হাজ্জ: হাদিসের সহজ শিক্ষা","explanation":"এই সহীহ হাদিসে একজন ব্যক্তি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কাছে এসে জিজ্ঞেস করেন, তার বাবা হাজ্জ না করেই মারা গেছেন; সে কি বাবার পক্ষ থেকে হাজ্জ করতে পারবে? রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) তাকে একটি সহজ উদাহরণ দেন। তিনি বলেন, যদি বাবার উপর ঋণ থাকত, তাহলে কি তুমি তা পরিশোধ করতে না? লোকটি হ্যাঁ বললে তিনি বাবার পক্ষ থেকে হাজ্জ করতে বলেন। এখানে মূল শিক্ষা হলো, মৃত ব্যক্তির দায়িত্বের বিষয়কে গুরুত্ব দেওয়া। “মৃত বাবার পক্ষ থেকে হাজ্জ” বা “বদলি হাজ্জের হাদিস” বিষয়ে এই বর্ণনা খুবই প্রাসঙ্গিক। হাদিসটি দেখায়, সন্তানের পক্ষে পিতার অনাদায় থাকা হাজ্জ আদায় করা একটি গুরুত্বপূর্ণ কাজ হতে পারে, যেমন ঋণ পরিশোধ করা দায়িত্বের বিষয়।","teachings":["মৃত বাবার অনাদায় থাকা হাজ্জের বিষয় গুরুত্বের সঙ্গে দেখা উচিত।","রাসূলুল্লাহ (সা.) ঋণ পরিশোধের উদাহরণ দিয়ে বিষয়টি বুঝিয়েছেন।","সন্তান পিতার পক্ষ থেকে কল্যাণকর কাজ করতে পারে।","ধর্মীয় দায়িত্বকে অবহেলা না করার শিক্ষা এতে আছে।"]},"searching_terms":["মৃত বাবার পক্ষ থেকে হাজ্জ","বদলি হাজ্জের হাদিস","মৃত ব্যক্তির পক্ষ থেকে হাজ্জ করা","বাবার জন্য হাজ্জ করা যাবে কি","হাজ্জ না করে মারা গেলে করণীয়","পিতার পক্ষ থেকে হাজ্জ","হাজ্জ ও ঋণ পরিশোধের হাদিস"],"related_hadiths":["সহীহ বুখারী ১৫১৩","সহীহ মুসলিম ১৩৩৪","সুনান আন-নাসায়ী ২৬৩৪ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>{"id":"25","core_topic":"আত্মীয়তা","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | আত্মীয়তার সম্পর্ক রক্ষার শেষ উপদেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. মৃত্যু শয্যায় আত্মীয়দের ব্যাপারে সতর্ক থাকার উপদেশ ও আত্মীয়তার সম্পর্ক না ছিন্ন করার শিক্ষা।"},"content":{"heading":"আত্মীয়তার সম্পর্ক রক্ষার গুরুত্ব: নবীজির উপদেশ","explanation":"এই সহীহ হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) মৃত্যু শয্যায় আত্মীয়দের ব্যাপারে সতর্ক থাকার কথা বলেন। বর্ণনায় কথাটি দুবার এসেছে, যা বিষয়টির গুরুত্ব বুঝায়। অর্থ হিসেবে বলা হয়েছে, আত্মীয়তার সম্পর্ক বজায় রাখো এবং তা ছিন্ন করো না। ইসলাম পরিবার ও আত্মীয়তার সম্পর্ককে শুধু সামাজিক বিষয় হিসেবে দেখে না; বরং এটি মানুষের আখলাক ও দায়িত্বের অংশ। “আত্মীয়তার সম্পর্ক রক্ষার হাদিস” বা “সিলাতুর রহিম” খুঁজলে এই হাদিসের মূল শিক্ষা হলো—আত্মীয়দের অধিকার ভুলে যাওয়া উচিত নয়। সম্পর্কের মধ্যে দূরত্ব, ভুল বোঝাবুঝি বা মনোমালিন্য থাকলেও সম্পর্ক পুরোপুরি ছিন্ন না করার চেষ্টা করা দরকার। হাদিসটি আমাদের পরিবারকেন্দ্রিক দায়িত্বের কথা মনে করিয়ে দেয়।","teachings":["আত্মীয়তার সম্পর্ক বজায় রাখা গুরুত্বপূর্ণ দায়িত্ব।","মনোমালিন্য হলেও সম্পর্ক ছিন্ন করা থেকে বাঁচা উচিত।","মৃত্যু শয্যার উপদেশ হিসেবে বিষয়টি বিশেষ গুরুত্ব পেয়েছে।","পরিবার ও আত্মীয়দের অধিকার অবহেলা করা ঠিক নয়।"]},"searching_terms":["আত্মীয়তার সম্পর্ক রক্ষার হাদিস","সিলাতুর রহিমের গুরুত্ব","আত্মীয়তা ছিন্ন করার ভয়","আত্মীয়দের অধিকার হাদিস","পরিবার সম্পর্কে নবীজির উপদেশ","আত্মীয়তার বন্ধন ইসলাম","সম্পর্ক বজায় রাখার হাদিস"],"related_hadiths":["সহীহ বুখারী ৫৯৮৪","সহীহ বুখারী ৫৯৮৮","সহীহ মুসলিম ২৫৫৫ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>{"id":"26","core_topic":"ক্ষমা","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | অনুগ্রহ, ক্ষমা ও কঠোর ভাষা থেকে বাঁচা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষের প্রতি অনুগ্রহ ও ক্ষমার শিক্ষা, আর কর্কশ ভাষা ও মন্দ কাজে অটল থাকার নিন্দা।"},"content":{"heading":"মানুষকে ক্ষমা করা ও কর্কশ ভাষা থেকে বাঁচার শিক্ষা","explanation":"এই সহীহ হাদিসে মানুষের সঙ্গে আচরণের কয়েকটি বড় শিক্ষা এসেছে। বলা হয়েছে, তোমরা অনুগ্রহ কর, তাহলে তোমাদের প্রতিও অনুগ্রহ করা হবে। তোমরা ক্ষমা কর, তাহলে আল্লাহ তোমাদের ক্ষমা করবেন। এরপর কর্কশভাষী মানুষ এবং যারা জেনে-শুনে নিজেদের মন্দ কাজের উপর অটল থাকে, তাদের জন্য ধ্বংসের সতর্কতা এসেছে। এখানে মূল বিষয় হলো ক্ষমা, দয়া, কোমল কথা ও ভুল থেকে ফিরে আসা। “ক্ষমা করার হাদিস” বা “কর্কশ ভাষা সম্পর্কে হাদিস” খুঁজলে এই বর্ণনা খুব সহজভাবে মানুষকে নিজের আচরণ দেখতে শেখায়। মানুষ ভুল করতে পারে, কিন্তু জেনে-শুনে খারাপ কাজে অটল থাকা বড় ক্ষতির কারণ। একইভাবে কষ্টদায়ক ভাষা মানুষের সম্পর্ক নষ্ট করে। তাই মুমিনের আচরণে দয়া, ক্ষমা ও নরম ভাষা থাকা উচিত।","teachings":["মানুষের প্রতি অনুগ্রহ ও দয়া করা ভালো চরিত্রের অংশ।","ক্ষমা করা আল্লাহর ক্ষমা লাভের কারণ হতে পারে।","কর্কশ ভাষা মানুষের জন্য ক্ষতির কারণ।","জেনে-শুনে মন্দ কাজে অটল থাকা থেকে বাঁচা উচিত।"]},"searching_terms":["ক্ষমা করার হাদিস","অনুগ্রহ করার হাদিস","কর্কশ ভাষা সম্পর্কে হাদিস","মানুষকে ক্ষমা কর আল্লাহ ক্ষমা করবেন","নরম ভাষার গুরুত্ব ইসলাম","মন্দ কাজে অটল থাকার ক্ষতি","আখলাক সম্পর্কে সহীহ হাদিস"],"related_hadiths":["জামে আত-তিরমিজি ১৯২৪","সুনান আবু দাউদ ৪৯৪১","সহীহ মুসলিম ২৫৮৮ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>{"id":"27","core_topic":"দাস অধিকার","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | দাস-দাসীদের অধিকার ও ভালো আচরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. দাস-দাসীদের খাবার, পোশাক, অধিকার রক্ষা এবং তাদের কষ্ট না দেওয়ার স্পষ্ট শিক্ষা।"},"content":{"heading":"দাস-দাসীদের অধিকার: খাবার, পোশাক ও কষ্ট না দেওয়ার শিক্ষা","explanation":"এই সহীহ হাদিসে বিদায় হাজ্জের দিনে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) দাস-দাসীদের ব্যাপারে বারবার সতর্ক করেছেন। তিনি বলেন, তোমরা তাদের ব্যাপারে সাবধান থেকো। অর্থ হিসেবে বলা হয়েছে, তাদের অধিকার আদায় করো, তাদের প্রতি অত্যাচার করো না এবং আল্লাহকে ভয় করো। এরপর বলা হয়েছে, তোমরা যা খাও তাদেরও তা খাওয়াও, তোমরা যা পর তাদেরও তা পরাও। যদি তারা এমন অপরাধ করে যা ক্ষমা করতে ইচ্ছা না হয়, তবে তাদের বিক্রি করবে; কিন্তু তাদের কষ্ট দেবে না। এই হাদিসের মূল শিক্ষা হলো অধীনস্থ মানুষের সঙ্গে ভালো ব্যবহার। “দাস-দাসীদের অধিকার” বা “খাদেমের অধিকার হাদিস” বিষয়ে এই বর্ণনা মানুষের দায়িত্ব পরিষ্কার করে। ক্ষমতার জায়গায় থেকেও অন্যের প্রতি জুলুম না করা মুমিনের চরিত্রের অংশ।","teachings":["অধীনস্থ মানুষের অধিকার রক্ষা করা জরুরি।","নিজে যা খায় ও পরে, তাদের ব্যাপারেও তা বিবেচনায় রাখা উচিত।","ক্ষমতার সুযোগে কাউকে কষ্ট দেওয়া থেকে বাঁচতে হবে।","অপরাধ হলেও অন্যায় শাস্তি দেওয়া ঠিক নয়।"]},"searching_terms":["দাস দাসীদের অধিকার হাদিস","খাদেমের অধিকার ইসলাম","তোমরা যা খাও তাদের খাওয়াও","অধীনস্থদের সাথে ভালো ব্যবহার","বিদায় হাজ্জের উপদেশ","দাসদের কষ্ট না দেওয়ার হাদিস","ইসলামে শ্রমিকের অধিকার"],"related_hadiths":["সহীহ বুখারী ২৫৪৫","সহীহ মুসলিম ১৬৬১","সুনান আবু দাউদ ৫১৫৭ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>{"id":"28","core_topic":"দাম্পত্য","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | দাম্পত্য জীবনে নিষিদ্ধ পথ থেকে সতর্কতা","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য কথা বলতে লজ্জা না করে স্ত্রীদের পায়ুপথ ব্যবহার না করার স্পষ্ট নিষেধাজ্ঞার শিক্ষা।"},"content":{"heading":"দাম্পত্য জীবনে পায়ুপথ ব্যবহার নিষেধ: হাদিসের শিক্ষা","explanation":"এই সহীহ হাদিসে দাম্পত্য জীবনের একটি স্পষ্ট নিষেধাজ্ঞা এসেছে। রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেছেন, তোমরা লজ্জা পোষণ করে থাক; আল্লাহ সত্য বলতে লজ্জা করেন না। এরপর তিনি স্ত্রীদের পায়ুপথ ব্যবহার করতে নিষেধ করেছেন। এখানে ভাষা সরাসরি, কারণ বিষয়টি শরিয়তের সীমার সঙ্গে জড়িত। “স্ত্রীর পায়ুপথ ব্যবহার নিষেধ” বা “দাম্পত্য জীবনের নিষিদ্ধ কাজ” বিষয়ে এই হাদিস মানুষকে বুঝায়, লজ্জার কারণে প্রয়োজনীয় সত্য কথা গোপন করা উচিত নয়। দাম্পত্য সম্পর্কেও আল্লাহর দেওয়া সীমা মানা দরকার। এই বর্ণনা থেকে অতিরিক্ত আলোচনা না বাড়িয়ে বলা যায়, হাদিসটি স্পষ্টভাবে একটি কাজ থেকে বারণ করেছে এবং সত্য বিষয় পরিষ্কারভাবে বলার শিক্ষা দিয়েছে।","teachings":["দাম্পত্য জীবনে শরিয়তের সীমা মানা জরুরি।","প্রয়োজনীয় সত্য কথা লজ্জার কারণে গোপন করা ঠিক নয়।","স্ত্রীদের পায়ুপথ ব্যবহার করা নিষিদ্ধ হিসেবে এসেছে।","ব্যক্তিগত বিষয়েও আল্লাহভীতি রাখা উচিত।"]},"searching_terms":["স্ত্রীর পায়ুপথ ব্যবহার নিষেধ হাদিস","দাম্পত্য জীবনের নিষিদ্ধ কাজ","আল্লাহ সত্য বলতে লজ্জা করেন না","স্ত্রীর সাথে সহবাসের আদব","পায়ুপথ সম্পর্কে হাদিস","ইসলামে দাম্পত্য বিধান","সহবাসে নিষিদ্ধ পথ"],"related_hadiths":["সুনান আবু দাউদ ২১৬২","জামে আত-তিরমিজি ১১৬৫","সুনান ইবনু মাজাহ ১৯২৩ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>{"id":"29","core_topic":"নম্রতা","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | নম্রতার বিনিময়ে নম্রতা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষের সঙ্গে নম্র আচরণ করলে নিজের প্রতিও নম্র আচরণের আশা করার সুন্দর শিক্ষা।"},"content":{"heading":"নম্রতার হাদিস: মানুষের সঙ্গে কোমল আচরণের শিক্ষা","explanation":"এই সহীহ হাদিসটি ছোট হলেও এর শিক্ষা খুব গভীর। আব্বাস (রাঃ) থেকে মারফূ সূত্রে বর্ণিত, “তুমি নম্রতা প্রদর্শন কর, তোমার প্রতি নম্রতা প্রদর্শন করা হবে।” এখানে মূল বিষয় হলো মানুষের সঙ্গে আচরণে কোমলতা। নম্রতা মানে দুর্বলতা নয়; বরং কথা, ব্যবহার ও সিদ্ধান্তে অহংকার কমানো। পরিবার, আত্মীয়, প্রতিবেশী বা সাধারণ মানুষের সঙ্গে কঠোরতা না দেখিয়ে নম্র আচরণ করলে সম্পর্ক সহজ হয়। “নম্রতার হাদিস” বা “কোমল আচরণের ফজিলত” খুঁজলে এই বর্ণনা খুব সহজভাবে আমাদের নিজের আচরণ যাচাই করতে শেখায়। মানুষ সাধারণত সেই আচরণই ফিরে পায়, যা সে অন্যের সঙ্গে করে। তাই মুমিনের ভাষা, মুখভঙ্গি ও ব্যবহার যেন নরম হয়—এটাই এই হাদিসের সরল বার্তা।","teachings":["মানুষের সঙ্গে নম্র আচরণ করা উচিত।","নম্রতা সম্পর্ককে সহজ ও সুন্দর করতে সাহায্য করে।","কঠোরতা নয়, কোমলতা ভালো চরিত্রের অংশ।","নিজের আচরণ অন্যের প্রতিক্রিয়াকে প্রভাবিত করতে পারে।"]},"searching_terms":["নম্রতার হাদিস","কোমল আচরণের হাদিস","মানুষের সাথে নম্র ব্যবহার","নম্রতার ফজিলত ইসলাম","আখলাক সম্পর্কে হাদিস","ভালো ব্যবহারের হাদিস","নরম কথার শিক্ষা"],"related_hadiths":["সহীহ মুসলিম ২৫৯৩","জামে আত-তিরমিজি ২০১৩","সুনান আবু দাউদ ৪৮০৭ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>{"id":"3","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতের ব্যাপারে তাড়াহুড়া না করা","description":"$book_name$ $hadith_number$ - $chapter_name$. কারো শেষ পরিণতি নিয়ে তাড়াহুড়া করে নিশ্চিত কথা না বলার নরম কিন্তু গুরুত্বপূর্ণ শিক্ষা এতে আছে।"},"content":{"heading":"জান্নাতের ব্যাপারে তাড়াহুড়া নয়: কথাবার্তায় সতর্কতার হাদিস","explanation":"এই হাদিসে কা’ব রাঃ-এর অসুস্থতার ঘটনা এসেছে। নাবী কারীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাঁকে দেখতে না পেয়ে জিজ্ঞেস করেন। সাহাবীরা জানান, তিনি অসুস্থ। এরপর রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম হেঁটে তাঁর কাছে যান এবং বলেন, হে কা’ব, সুসংবাদ গ্রহণ কর। কা’বের মা তখন জান্নাতের অভিনন্দন জানান। কিন্তু রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেন, আল্লাহর ফায়সালার ব্যাপারে এই তাড়াহুড়াকারিণী কে? এরপর তিনি মনে করিয়ে দেন, মানুষ এমন কথা বলতে পারে যা তার জন্য ঠিক নয়, অথবা এমন বিষয়ে চুপ থাকতে পারে যেখানে চুপ থাকা ক্ষতির কারণ নয়। হাদিসটি হাসান বলা হয়েছে। এই বর্ণনা জান্নাত, কথা সংযম এবং আল্লাহর ফায়সালার ব্যাপারে সতর্ক থাকার শিক্ষা দেয়।","teachings":["কারো আখিরাতের ফল নিয়ে নিশ্চিত দাবি করতে তাড়াহুড়া করা ঠিক নয়।","অসুস্থ মুসলিমকে দেখতে যাওয়া সুন্দর আচরণের অংশ।","কথা বলা ও চুপ থাকার ক্ষেত্রেও মানুষকে সতর্ক হতে হয়।","আল্লাহর ফায়সালা সম্পর্কে বিনয়ী থাকা উচিত।"]},"searching_terms":["কা’বের অসুস্থতার হাদিস","জান্নাতের ব্যাপারে তাড়াহুড়া হাদিস","আল্লাহর ফয়সালা হাদিস","কথা সংযম হাদিস","সিলসিলা সহিহা ৩","অসুস্থকে দেখতে যাওয়ার হাদিস"],"related_hadiths":["সিলসিলা সহিহা ১৪","সিলসিলা সহিহা ৫","সিলসিলা সহিহা ১০ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>{"id":"30","core_topic":"জান্নাত","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | ছয়টি আমল ও জান্নাতের নিশ্চয়তা","description":"$book_name$ $hadith_number$ - $chapter_name$. সত্য কথা, ওয়াদা পালন, আমানত আদায়, লজ্জাস্থান হিফাজত, দৃষ্টি ও হাত সংযত রাখার শিক্ষা।"},"content":{"heading":"জান্নাতের নিশ্চয়তার ছয়টি আমল","explanation":"এই হাসান হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) ছয়টি বিষয়ের নিশ্চয়তা চাইলে জান্নাতের নিশ্চয়তার কথা বলেছেন। এগুলো হলো: কথা বললে সত্য বলা, ওয়াদা করলে তা পালন করা, আমানত গ্রহণ করলে তা আদায় করা, লজ্জাস্থানের হিফাজত করা, দৃষ্টি অবনত রাখা এবং হাতকে অন্যায় কাজ থেকে সংযত রাখা। এই হাদিসে ঈমানদারের দৈনন্দিন চরিত্রের বড় ভিত্তিগুলো একসঙ্গে এসেছে। “ছয়টি আমলের হাদিস” বা “জান্নাতের নিশ্চয়তার হাদিস” বিষয়ে এটি খুব গুরুত্বপূর্ণ। এখানে শুধু ইবাদতের কথা নয়; কথা, প্রতিশ্রুতি, আমানত, চোখ, লজ্জাস্থান ও হাত—সবকিছুর নিয়ন্ত্রণের কথা আছে। অর্থাৎ একজন মুমিনের সততা, পবিত্রতা ও অন্যায় থেকে বিরত থাকার জীবনই তাকে আল্লাহর সন্তুষ্টির পথে রাখে।","teachings":["কথা বললে সত্য বলা মুমিনের বড় গুণ।","ওয়াদা ও আমানত রক্ষা করা জরুরি দায়িত্ব।","চোখ, হাত ও লজ্জাস্থানকে অন্যায় থেকে সংযত রাখতে হবে।","জান্নাতের পথ চরিত্র ও আচরণের সঙ্গেও জড়িত।"]},"searching_terms":["ছয়টি আমলের হাদিস","জান্নাতের নিশ্চয়তার হাদিস","সত্য কথা বলা ওয়াদা পালন হাদিস","আমানত আদায়ের হাদিস","দৃষ্টি অবনত রাখার হাদিস","লজ্জাস্থান হিফাজতের হাদিস","উবাদাহ রাঃ ছয়টি জিনিস"],"related_hadiths":["সহীহ বুখারী ৬৪৭৪","সহীহ বুখারী ৬০৯৪","সহীহ মুসলিম ২৬০৭ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>{"id":"31","core_topic":"পিতামাতা","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | পিতার আনুগত্য ও তালাকের ঘটনা","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবনু উমরের স্ত্রীর ঘটনা, উমর (রাঃ)-এর নির্দেশ এবং পিতার আনুগত্যের শিক্ষা।"},"content":{"heading":"পিতার আনুগত্য: ইবনু উমরের তালাকের ঘটনার শিক্ষা","explanation":"এই হাসান হাদিসে ইবনু উমর (রাঃ)-এর একটি ব্যক্তিগত ঘটনা এসেছে। তাঁর এক স্ত্রী ছিলেন, যাকে তিনি ভালোবাসতেন। কিন্তু উমর (রাঃ) তাকে অপছন্দ করতেন এবং ইবনু উমরকে তালাক দিতে বলেন। ইবনু উমর প্রথমে অস্বীকৃতি জানান। পরে বিষয়টি নাবী (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-কে জানানো হলে তিনি বলেন, “তোমার পিতার আনুগত্য কর এবং তাকে তালাক দাও।” এখানে মূল বিষয় পিতার আনুগত্য; তবে হাদিসের পাঠ অনুযায়ী ঘটনাটি নির্দিষ্ট ব্যক্তির নির্দিষ্ট পরিস্থিতির সঙ্গে যুক্ত। তাই এটিকে সাধারণভাবে সব অবস্থায় পিতার কথায় তালাক বাধ্যতামূলক—এভাবে বাড়িয়ে বলা ঠিক নয়। “পিতার আনুগত্যের হাদিস” বা “ইবনু উমরের তালাকের ঘটনা” খুঁজলে এই বর্ণনা দেখায়, সাহাবীরা পারিবারিক বিষয়ে নবীজির নির্দেশকে গুরুত্ব দিতেন।","teachings":["পিতামাতার কথা গুরুত্ব দিয়ে শোনা উচিত।","পারিবারিক বিষয়ে আবেগের পাশাপাশি দ্বীনি নির্দেশও বিবেচ্য।","হাদিসটি একটি নির্দিষ্ট ঘটনার বর্ণনা; অতিরিক্ত সাধারণীকরণ করা ঠিক নয়।","সাহাবীরা নবীজির নির্দেশ মেনে চলতেন।"]},"searching_terms":["ইবনু উমরের স্ত্রী তালাকের ঘটনা","পিতার আনুগত্যের হাদিস","উমর রাঃ পুত্রকে তালাকের নির্দেশ","মা বাবার আনুগত্য ইসলাম","তালাক ও পিতার কথা","আস সহীহাহ ৯১৯","পিতামাতার হক হাদিস"],"related_hadiths":["জামে আত-তিরমিজি ১১৮৯","সুনান আবু দাউদ ৫১৩৮","সুনান ইবনু মাজাহ ২০৮৮ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>{"id":"32","core_topic":"উপদেশ","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | তাওহীদ, সৎকাজ ও উত্তম আচরণের উপদেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. আল্লাহর ইবাদাত, শিরক থেকে বাঁচা, মন্দের পর সৎ কাজ করা ও উত্তম আচরণের শিক্ষা।"},"content":{"heading":"মুয়াজ (রাঃ)-কে নবীজির উপদেশ: তাওহীদ ও উত্তম আচরণ","explanation":"এই হাসান হাদিসে মুয়াজ ইবনু জাবাল (রাঃ) সফরে যাওয়ার আগে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কাছে উপদেশ চান। নবীজি প্রথমে বলেন, আল্লাহর ইবাদাত কর এবং তাঁর সঙ্গে কাউকে শরীক করো না। এরপর আরো উপদেশ চাইলে বলেন, কোনো মন্দ কাজ করলে তার বদলে সৎ কাজ করো। আবার আরো নসীহত চাইলে বলেন, এগুলোর উপর অটল থাক এবং তোমার আচরণ উত্তম কর। এই হাদিসে তাওহীদ, তাওবা, সৎ কাজ ও ভালো চরিত্র—চারটি গুরুত্বপূর্ণ শিক্ষা এসেছে। “মুয়াজ রাঃ উপদেশ” বা “মন্দ কাজের পর সৎ কাজ” বিষয়ে এটি খুব সহজ কিন্তু গভীর বর্ণনা। মানুষের ভুল হতে পারে, কিন্তু ভুলের পর সৎ কাজ করা এবং উত্তম আচরণে অটল থাকা মুমিনের পথ।","teachings":["আল্লাহর ইবাদাত ও শিরক থেকে বাঁচা মূল ভিত্তি।","মন্দ কাজ হয়ে গেলে সৎ কাজের দিকে ফিরে আসা উচিত।","দ্বীনের পথে অটল থাকা প্রয়োজন।","উত্তম আচরণ ইসলামী জীবনের গুরুত্বপূর্ণ অংশ।"]},"searching_terms":["মুয়াজ রাঃ উপদেশ","মন্দ কাজের পর সৎ কাজ","আল্লাহর ইবাদাত কর শিরক করো না","উত্তম আচরণের হাদিস","নবীজির নসীহত","তাওহীদ সম্পর্কে হাদিস","আস সহীহাহ ১২২৮"],"related_hadiths":["জামে আত-তিরমিজি ১৯৮৭","জামে আত-তিরমিজি ২৫১৬","সুনান আদ-দারিমী ২৭৯১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>{"id":"33","core_topic":"আত্মীয়তা","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | বংশপরিচয় জানা ও আত্মীয়তা রক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. বংশপরিচয় জেনে আত্মীয়তার বন্ধন মজবুত রাখা এবং সম্পর্ক ছিন্ন না করার শিক্ষা।"},"content":{"heading":"বংশপরিচয় জানার উদ্দেশ্য: আত্মীয়তার বন্ধন রক্ষা","explanation":"এই সহীহ হাদিসে বংশপরিচয় জানার একটি সুন্দর উদ্দেশ্য বলা হয়েছে। বর্ণনায় দেখা যায়, ইবনু আব্বাস (রাঃ)-এর কাছে একজন ব্যক্তি এলে তিনি দূর সম্পর্কের আত্মীয়তা খুঁজে পান এবং তার সঙ্গে নম্রভাবে কথা বলেন। এরপর রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর বাণী উল্লেখ করা হয়: তোমরা তোমাদের বংশ পরম্পরা জেনে রেখো এবং আত্মীয়তার বন্ধন সুদৃঢ় রেখো। কারণ সম্পর্ক ছিন্ন হলে নিকট আত্মীয়ও নিকট থাকে না; আর সম্পর্ক বজায় থাকলে দূর আত্মীয়ও দূর থাকে না। “বংশপরিচয় জানার হাদিস” বা “আত্মীয়তার বন্ধন রক্ষার হাদিস” খুঁজলে এই বর্ণনা স্পষ্ট করে যে বংশ জানা অহংকারের জন্য নয়; বরং সম্পর্ক বজায় রাখার জন্য। আত্মীয়তার মূল্য সম্পর্ক রক্ষার মধ্যেই প্রকাশ পায়।","teachings":["বংশপরিচয় জানার উদ্দেশ্য আত্মীয়তা রক্ষা হওয়া উচিত।","সম্পর্ক ছিন্ন হলে নিকট আত্মীয়ও দূরে চলে যেতে পারে।","সম্পর্ক বজায় রাখলে দূর আত্মীয়ও আপন হয়ে থাকে।","আত্মীয়ের সঙ্গে নম্র আচরণ করা ভালো চরিত্রের অংশ।"]},"searching_terms":["বংশপরিচয় জানার হাদিস","আত্মীয়তার বন্ধন রক্ষা","সিলাতুর রহিম হাদিস","বংশ পরম্পরা জেনে রাখো","দূর আত্মীয় সম্পর্কে হাদিস","আত্মীয়তা ছিন্ন করার ক্ষতি","ইবনু আব্বাস আত্মীয়তা"],"related_hadiths":["জামে আত-তিরমিজি ১৯৭৯","সহীহ বুখারী ৫৯৮৪","সহীহ মুসলিম ২৫৫৫ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>{"id":"34","core_topic":"ক্ষমা","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | খাদেমকে ক্ষমা করার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদেমকে কতবার ক্ষমা করা হবে—এই প্রশ্নে দৈনিক সত্তরবার ক্ষমার সুন্দর শিক্ষা।"},"content":{"heading":"খাদেমকে ক্ষমা করার হাদিস: দৈনিক সত্তরবারের শিক্ষা","explanation":"এই হাসান হাদিসে একজন ব্যক্তি রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম)-এর কাছে জিজ্ঞেস করেন, খাদেমকে কতবার ক্ষমা করা হবে? নবীজি প্রথমে নীরব থাকেন। লোকটি আবার প্রশ্ন করলে তিনি তখনও চুপ থাকেন। তৃতীয়বার প্রশ্ন করা হলে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেন, দৈনিক সত্তরবার তাকে ক্ষমা কর। এখানে “সত্তরবার” কথাটি খাদেমের ভুলের প্রতি ধৈর্য ও ক্ষমাশীলতার শক্ত বার্তা দেয়। “খাদেমকে ক্ষমা করার হাদিস” বা “অধীনস্থদের সাথে ভালো ব্যবহার” বিষয়ে এই বর্ণনা খুবই প্রয়োজনীয়। যারা আমাদের সেবা করে বা অধীনে কাজ করে, তাদের ভুল হলে সঙ্গে সঙ্গে কঠোর হওয়া উচিত নয়। ক্ষমা, ধৈর্য ও সুন্দর আচরণ মুমিনের চরিত্রকে উজ্জ্বল করে।","teachings":["খাদেম বা অধীনস্থের ভুলে ধৈর্য ধরা উচিত।","ক্ষমাশীলতা ভালো চরিত্রের গুরুত্বপূর্ণ অংশ।","বারবার প্রশ্নের পর উত্তর দেওয়া বিষয়টির গুরুত্ব বোঝায়।","ক্ষমতা থাকলেও কঠোরতা না দেখানো উত্তম।"]},"searching_terms":["খাদেমকে ক্ষমা করার হাদিস","দৈনিক সত্তরবার ক্ষমা","অধীনস্থদের সাথে ভালো ব্যবহার","খাদেমের অধিকার ইসলাম","ক্ষমাশীলতার হাদিস","সেবকের ভুল ক্ষমা করা","আস সহীহাহ ৪৮৮"],"related_hadiths":["সুনান আবু দাউদ ৫১৬৪","জামে আত-তিরমিজি ১৯৪৯","সহীহ মুসলিম ১৬৬১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>{"id":"35","core_topic":"সালাম","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | সালাম, খাবার দেওয়া ও উত্তম আচরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. সালামের প্রসার, মানুষকে খাবার দেওয়া, আল্লাহর সামনে লজ্জা ও ভুলের পর সৎ কাজের শিক্ষা।"},"content":{"heading":"সালামের প্রসার ও খাবার বিতরণের হাদিস","explanation":"এই হাসান লিগাইরিহী হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) একজন প্রতিনিধিকে গুরুত্বপূর্ণ কিছু উপদেশ দেন। তিনি বলেন, সালামের প্রসার ঘটাবে এবং খাবার বিতরণ করবে। আরও বলেন, পরিবারের লোকদের ব্যাপারে যেমন লজ্জা করা হয়, তেমনি আল্লাহর ব্যাপারে লজ্জা করবে। কোনো ত্রুটি হলে তার বিনিময়ে সৎ কাজ করবে এবং যতটুকু সম্ভব আচরণ উত্তম করবে। এই হাদিসে সামাজিক আচরণ ও ব্যক্তিগত তাকওয়ার সুন্দর মিল আছে। “সালাম ছড়ানোর হাদিস” বা “খাবার খাওয়ানোর ফজিলত” খুঁজলে এই বর্ণনা খুব প্রাসঙ্গিক। সালাম মানুষের মধ্যে নিরাপত্তা ও ভালোবাসা বাড়ায়। খাবার দেওয়া মানুষের প্রয়োজন পূরণ করে। আর ভুলের পর সৎ কাজ করা মানুষকে সংশোধনের পথে রাখে। সব মিলিয়ে এটি সহজ, বাস্তব ও সুন্দর জীবনযাপনের শিক্ষা।","teachings":["সালাম ছড়ানো মুসলিম সমাজে ভালোবাসা বাড়ায়।","মানুষকে খাবার দেওয়া উত্তম সামাজিক কাজ।","আল্লাহর সামনে লজ্জা ও দায়িত্ববোধ থাকা উচিত।","ত্রুটি হলে সৎ কাজের মাধ্যমে সংশোধনের চেষ্টা করা ভালো।"]},"searching_terms":["সালাম ছড়ানোর হাদিস","খাবার খাওয়ানোর ফজিলত","ভুলের পর সৎ কাজ","আল্লাহর ব্যাপারে লজ্জা","উত্তম আচরণের হাদিস","সালাম ও খাবার বিতরণ","আস সহীহাহ ৩৫৫৯"],"related_hadiths":["সহীহ বুখারী ১২","সহীহ মুসলিম ৫৪","জামে আত-তিরমিজি ২৪৮৫ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>{"id":"36","core_topic":"সদাচরণ","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | হাসিমুখে সাক্ষাৎ ও ভাইয়ের উপকার","description":"$book_name$ $hadith_number$ - $chapter_name$. ভাইয়ের সঙ্গে প্রফুল্লচিত্তে সাক্ষাৎ, ঋণ পরিশোধে সাহায্য ও আহার করানোর শিক্ষা।"},"content":{"heading":"হাসিমুখে সাক্ষাৎ ও ভাইয়ের প্রয়োজন পূরণের আমল","explanation":"এই হাসান হাদিসে কিছু সহজ অথচ মূল্যবান আমলের কথা বলা হয়েছে। আবু হুরাইরাহ (রাঃ) থেকে মারফূ সূত্রে বর্ণিত, সার্বোত্তম আমল হলো—তোমার ভাইয়ের সঙ্গে প্রফুল্লচিত্তে সাক্ষাৎ করা, তার ঋণ পরিশোধ করা এবং তাকে রুটি বা আহার্যদ্রব্য খাওয়ানো। এখানে “ভাই” বলতে মুসলিম ভাইয়ের সঙ্গে সুন্দর সম্পর্কের দিকটি বোঝানো হয়েছে। “হাসিমুখে সাক্ষাতের হাদিস” বা “ভাইকে খাবার খাওয়ানোর ফজিলত” বিষয়ে এই হাদিস মানুষকে ছোট ছোট ভালো কাজের দিকে টানে। কারও সঙ্গে হাসিমুখে দেখা করা, তার আর্থিক কষ্ট কমাতে সাহায্য করা এবং তাকে খাবার দেওয়া—এসব কাজ সমাজে মমতা ও ভ্রাতৃত্ব বাড়ায়। হাদিসটি আমাদের শেখায়, ভালো আমল শুধু বড় কাজেই সীমাবদ্ধ নয়; সহজ ব্যবহারও মূল্যবান হতে পারে।","teachings":["মুসলিম ভাইয়ের সঙ্গে হাসিমুখে সাক্ষাৎ করা ভালো আমল।","কারও ঋণ পরিশোধে সাহায্য করা বড় উপকার।","অন্যকে খাবার দেওয়া সামাজিক কল্যাণের কাজ।","সুন্দর আচরণও আমলের অংশ।"]},"searching_terms":["হাসিমুখে সাক্ষাতের হাদিস","ভাইকে খাবার খাওয়ানোর ফজিলত","ঋণ পরিশোধে সাহায্যের হাদিস","প্রফুল্লচিত্তে সাক্ষাৎ","সদাচরণ সম্পর্কে হাদিস","মুসলিম ভাইয়ের উপকার","সার্বোত্তম আমল হাদিস"],"related_hadiths":["জামে আত-তিরমিজি ১৯৫৬","সহীহ মুসলিম ২৬২৬","সহীহ বুখারী ১২ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>{"id":"37","core_topic":"সমঝোতা","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | মানুষের মাঝে সমঝোতার সাদাকা","description":"$book_name$ $hadith_number$ - $chapter_name$. মানুষের বিরোধ মিটিয়ে পরস্পরের মাঝে সমঝোতা করাকে উত্তম সাদাকা হিসেবে দেখার শিক্ষা।"},"content":{"heading":"সমঝোতা করানো: সর্বোত্তম সাদাকার শিক্ষা","explanation":"এই হাসান লিগাইরিহী হাদিসে বলা হয়েছে, সর্বোত্তম সাদাকা হলো পরস্পরের মাঝে সমঝোতা করা। সাধারণত সাদাকা শুনলে আমরা টাকা-পয়সা বা খাবার দানের কথা ভাবি। কিন্তু এই হাদিস মানুষের সম্পর্ক ঠিক করে দেওয়া, মনোমালিন্য কমানো এবং ঝগড়া মিটিয়ে দেওয়ার মূল্য বুঝায়। “সমঝোতা করানোর হাদিস” বা “মানুষের মাঝে মীমাংসা” বিষয়ে এই বর্ণনা খুব দরকারি। দুই পক্ষের মধ্যে ভুল বোঝাবুঝি হলে আগুনে ঘি ঢালা নয়; বরং ন্যায় ও শান্তির পথে মিল করানোর চেষ্টা করা ভালো কাজ। তবে সমঝোতা করাতে গিয়ে সত্য গোপন করে অন্যায়কে সমর্থন করা ঠিক নয়—এই সতর্কতা সাধারণ ইসলামী নীতির সঙ্গে যুক্ত। হাদিসের মূল শিক্ষা হলো, সম্পর্ক জোড়া লাগানো সমাজের জন্য কল্যাণকর আমল।","teachings":["মানুষের মাঝে সমঝোতা করানো সাদাকার মতো মূল্যবান কাজ।","ঝগড়া বাড়ানো নয়, শান্তির পথ খোঁজা উচিত।","সম্পর্ক ঠিক করা সামাজিক কল্যাণের অংশ।","মীমাংসায় ন্যায় ও সততার দিকে খেয়াল রাখা দরকার।"]},"searching_terms":["সমঝোতা করানোর হাদিস","সর্বোত্তম সাদাকা সমঝোতা","মানুষের মাঝে মীমাংসা","সম্পর্ক ঠিক করার হাদিস","ঝগড়া মিটানোর ইসলামিক উপায়","সাদাকা সম্পর্কে হাদিস","আস সহীহাহ ২৬৩৯"],"related_hadiths":["সহীহ বুখারী ২৬৯২","সুনান আবু দাউদ ৪৯১৯","জামে আত-তিরমিজি ২৫০৯ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>{"id":"38","core_topic":"গীবত","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | গীবতের ভয় ও ক্ষমা চাওয়ার শিক্ষা","description":"$book_name$ $hadith_number$ - $chapter_name$. খাদেমকে নিয়ে কথা বলার ঘটনায় গীবতের ভয়াবহতা ও যার গীবত হয়েছে তার কাছে ক্ষমা চাওয়ার শিক্ষা।"},"content":{"heading":"গীবতের ভয়াবহতা: ভাইয়ের গোশত খাওয়ার উপমা","explanation":"এই সহীহ হাদিসে গীবতের ভয়াবহতা একটি স্পষ্ট ঘটনার মাধ্যমে বোঝানো হয়েছে। আবু বকর ও উমর (রাঃ)-এর সঙ্গে সফরে একজন খাদেম ছিলেন। তিনি ঘুমিয়ে পড়ায় খাবার প্রস্তুত করতে পারেননি। তখন তাঁকে নিয়ে এমন কথা বলা হয়, যা পরে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) খুব কঠিনভাবে ধরিয়ে দেন। যখন তারা খাবার চাইলেন, নবীজি বলেন, তারা তো খাবার গ্রহণ করেছে। পরে তিনি ব্যাখ্যা করেন, তারা তাদের ভাইয়ের গোশত খেয়েছে। অর্থাৎ গীবতকে খুব ভয়ংকর কাজ হিসেবে দেখানো হয়েছে। তারা ক্ষমা চাইলে নবীজি বলেন, সে তোমাদের ক্ষমা করবে। “গীবতের হাদিস” বা “ভাইয়ের গোশত খাওয়ার হাদিস” বিষয়ে এই বর্ণনা মানুষকে জিহ্বার ব্যাপারে সতর্ক করে। কারও অনুপস্থিতিতে তাকে ছোট করা সম্পর্ক ও আখলাক নষ্ট করে।","teachings":["কারও অনুপস্থিতিতে তাকে ছোট করে কথা বলা ভয়ংকর গুনাহ।","খাদেম বা অধীনস্থের ভুল নিয়ে অপমানজনক কথা বলা ঠিক নয়।","গীবত হলে যার গীবত করা হয়েছে তার কাছেও ক্ষমা চাওয়া দরকার।","জিহ্বা সংযত রাখা মুমিনের গুরুত্বপূর্ণ দায়িত্ব।"]},"searching_terms":["গীবতের হাদিস","ভাইয়ের গোশত খাওয়ার হাদিস","গীবত করলে কী হয়","অন্যের দোষ বলা হাদিস","খাদেমকে নিয়ে গীবত","জিহ্বা সংযত রাখার হাদিস","আস সহীহাহ ২৬০৮"],"related_hadiths":["সহীহ মুসলিম ২৫৮৯","সুনান আবু দাউদ ৪৮৭৪","জামে আত-তিরমিজি ১৯৩৪ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>{"id":"39","core_topic":"উত্তম চরিত্র","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | পরিপূর্ণ ঈমান ও উত্তম চরিত্র","description":"$book_name$ $hadith_number$ - $chapter_name$. উত্তম চরিত্র, নম্র স্বভাব, অতিথিপরায়ণতা ও ভালোবাসার মাধ্যমে ঈমানের পূর্ণতার শিক্ষা।"},"content":{"heading":"পরিপূর্ণ ঈমানের পরিচয়: উত্তম চরিত্র ও ভালোবাসা","explanation":"এই হাসান হাদিসে মুমিনের পরিপূর্ণ ঈমানের সঙ্গে উত্তম চরিত্রকে যুক্ত করা হয়েছে। বলা হয়েছে, মুমিনদের মধ্যে পরিপূর্ণ ঈমানদার সেই ব্যক্তি, যে চরিত্রে উত্তম, নম্র স্বভাবের, অতিথিপরায়ণ, অন্যকে ভালোবাসে এবং অন্যের ভালোবাসা পায়। এরপর বলা হয়েছে, যারা অন্যকে ভালোবাসে না এবং অন্যের ভালোবাসাও পায় না, তাদের মধ্যে কল্যাণ নেই। এখানে মূল বিষয় হলো আখলাক, নম্রতা, অতিথি সেবা ও মানুষের সঙ্গে ভালো সম্পর্ক। “পরিপূর্ণ ঈমানদার কে” বা “উত্তম চরিত্রের হাদিস” খুঁজলে এই বর্ণনা খুব পরিষ্কারভাবে বলে—ঈমান শুধু মুখের দাবি নয়; আচরণেও তার প্রভাব দেখা যায়। ভালোবাসা দেওয়া ও গ্রহণ করার মতো চরিত্র একজন মুমিনকে মানুষের জন্য উপকারী করে তোলে।","teachings":["উত্তম চরিত্র ঈমানের পূর্ণতার গুরুত্বপূর্ণ চিহ্ন।","নম্র স্বভাব ও অতিথিপরায়ণতা প্রশংসনীয় গুণ।","মানুষকে ভালোবাসা এবং ভালোবাসা পাওয়ার মতো আচরণ করা উচিত।","কঠিন ও অমিশুক আচরণ কল্যাণ কমিয়ে দিতে পারে।"]},"searching_terms":["পরিপূর্ণ ঈমানদার কে","উত্তম চরিত্রের হাদিস","নম্র স্বভাবের হাদিস","অতিথিপরায়ণতার হাদিস","ভালোবাসা সম্পর্কে হাদিস","ঈমান ও আখলাক","আস সহীহাহ ৭৫১"],"related_hadiths":["সুনান আবু দাউদ ৪৬৮২","জামে আত-তিরমিজি ১১৬২","সহীহ বুখারী ৬০৩৫ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+    <row r="32" ht="46" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>{"id":"4","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | অতি ঝগড়াটে স্বভাবের ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. অতি ঝগড়াটে মানুষ আল্লাহর নিকট নিকৃষ্ট—এই হাদিসে ঝগড়া এড়ানোর কড়া শিক্ষা এসেছে।"},"content":{"heading":"অতি ঝগড়াটে ব্যক্তি: চরিত্র সংশোধনের গুরুত্বপূর্ণ হাদিস","explanation":"এই হাদিসে নাবী কারীম সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, অতি ঝগড়াটে ব্যক্তি আল্লাহর নিকট সর্বাপেক্ষা নিকৃষ্ট ব্যক্তি। কথাটি খুব ছোট, কিন্তু এর শিক্ষা বড়। ঝগড়া মানুষের সম্পর্ক নষ্ট করে, কথা কঠিন করে এবং মনকে রাগের দিকে নিয়ে যায়। এখানে সাধারণ মতভেদ নয়, বরং অতি ঝগড়াটে স্বভাবের কথা বলা হয়েছে। অর্থাৎ যে মানুষ অকারণে বা বেশি বেশি তর্কে জড়ায়, তার চরিত্রের মধ্যে বড় সমস্যা থাকে। হাদিসটি সহীহ বলা হয়েছে। তাই মুসলিম জীবনে ঝগড়া এড়ানো, নরম কথা বলা এবং নিজের রাগ সামলানো খুব দরকার। অতি ঝগড়াটে ব্যক্তি হাদিস আমাদের শেখায়, সত্য কথা বলার সময়ও আচরণ সুন্দর রাখা উচিত।","teachings":["অতি ঝগড়াটে স্বভাব আল্লাহর নিকট অপছন্দনীয়।","মতভেদ হলে তর্ক বাড়িয়ে না দিয়ে সংযম রাখা উচিত।","ঝগড়া মানুষের সম্পর্ক দুর্বল করতে পারে।","ভালো চরিত্রের জন্য কথা ও রাগ নিয়ন্ত্রণ জরুরি।"]},"searching_terms":["অতি ঝগড়াটে ব্যক্তি হাদিস","আল্লাহর নিকট নিকৃষ্ট ব্যক্তি","ঝগড়া নিয়ে হাদিস","সিলসিলা সহিহা ৪","তর্ক ঝগড়া ইসলাম","চরিত্র সংশোধন হাদিস"],"related_hadiths":["সিলসিলা সহিহা ১০","সিলসিলা সহিহা ১৪","সিলসিলা সহিহা ৫ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>{"id":"40","core_topic":"দাম্পত্য","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | স্ত্রীদের সঙ্গে উত্তম আচরণ","description":"$book_name$ $hadith_number$ - $chapter_name$. পরিপূর্ণ ঈমানের পরিচয় উত্তম চরিত্র, আর স্ত্রীর কাছে ভালো হওয়া সর্বোত্তমতার শিক্ষা।"},"content":{"heading":"স্ত্রীর কাছে ভালো হওয়া: উত্তম চরিত্রের হাদিস","explanation":"এই হাসান হাদিসে রাসূলুল্লাহ (সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম) বলেন, মুমিনদের মধ্যে পরিপূর্ণ ঈমানদার সেই ব্যক্তি, যে চরিত্রে সর্বাপেক্ষা উত্তম। এরপর বলেন, তোমাদের মধ্যে সর্বোত্তম সে, যে তার স্ত্রীর কাছে সবচেয়ে ভালো। এখানে ঈমান, আখলাক ও দাম্পত্য আচরণকে একসঙ্গে রাখা হয়েছে। একজন মানুষ বাইরে ভালো ব্যবহার করলেও ঘরের ভেতরে তার আচরণই তার চরিত্রের বড় পরীক্ষা। “স্ত্রীর সাথে ভালো আচরণের হাদিস” বা “সর্বোত্তম ব্যক্তি তার স্ত্রীর কাছে ভালো” বিষয়ে এই বর্ণনা খুব পরিচিত ও শিক্ষণীয়। হাদিসটি স্বামীকে স্মরণ করিয়ে দেয়, স্ত্রীর প্রতি দয়া, সম্মান, নরম কথা ও ভালো ব্যবহার মুমিনের চরিত্রের অংশ। ভালো দাম্পত্য শুধু সামাজিক সম্পর্ক নয়; এটি দ্বীনি আখলাকের বাস্তব প্রকাশ।","teachings":["উত্তম চরিত্র ঈমানের পূর্ণতার সঙ্গে যুক্ত।","স্ত্রীর সঙ্গে ভালো ব্যবহার করা বড় গুণ।","ঘরের আচরণ মানুষের চরিত্রের গুরুত্বপূর্ণ পরিচয়।","দাম্পত্য সম্পর্কে সম্মান ও কোমলতা রাখা উচিত।"]},"searching_terms":["স্ত্রীর সাথে ভালো আচরণের হাদিস","সর্বোত্তম ব্যক্তি তার স্ত্রীর কাছে ভালো","পরিপূর্ণ ঈমানদার হাদিস","উত্তম চরিত্রের হাদিস","স্বামীর দায়িত্ব হাদিস","দাম্পত্য জীবনের আখলাক","আস সহীহাহ ২৮৪"],"related_hadiths":["জামে আত-তিরমিজি ১১৬২","সুনান আবু দাউদ ৪৬৮২","সুনান ইবনু মাজাহ ১৯৭৭ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>{"id":"41","meta_data":{"title":"$book_name$ - 41 ($publication$) | নম্র স্বভাব ও জাহান্নামের আগুন থেকে বাঁচার শিক্ষা","description":"$book_name$ 41 - $chapter_name$. নম্র, শান্ত ও হিতৈষী আচরণ মানুষের চরিত্রকে সুন্দর করে এবং জাহান্নামের আগুন থেকে বাঁচার কারণ হতে পারে।"},"content":{"heading":"নম্র স্বভাবের ফজিলত: শান্ত ও হিতৈষী চরিত্রের হাদিস","explanation":"এই হাদিসে রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম এমন মানুষের কথা বলেছেন, যার জন্য জাহান্নামের আগুন হারাম হতে পারে। এখানে মূল শিক্ষা হলো নম্র স্বভাব, শান্ত আচরণ এবং মানুষের কল্যাণ চাওয়া। একজন হিতৈষী মানুষ অন্যের ক্ষতি চায় না, কথা ও কাজে সহজ থাকে এবং রাগ বা কঠোরতার বদলে কোমল পথ বেছে নেয়। হাদিসটি আমাদের শেখায়, উত্তম চরিত্র শুধু বাহ্যিক ভদ্রতা নয়; বরং অন্তরের কোমলতা ও মানুষের প্রতি ভালো মনোভাবও এর অংশ। তাই পরিবার, সমাজ ও দৈনন্দিন লেনদেনে নম্রতা ধরে রাখা মুমিনের জন্য বড় গুণ।","teachings":["মানুষের প্রতি হিতৈষী মনোভাব রাখা উত্তম চরিত্রের অংশ।","নম্র ও শান্ত আচরণ আখিরাতের কল্যাণের কারণ হতে পারে।","কঠোরতা নয়, কোমলতা মুমিনের আচরণকে সুন্দর করে।","অন্যের উপকার চাওয়া ও সহজ ব্যবহার করা ইসলামের পছন্দনীয় শিক্ষা।"]},"searching_terms":["নম্র স্বভাবের হাদিস","জাহান্নামের আগুন হারাম হাদিস","হিতৈষী শান্ত নম্র ব্যক্তি","উত্তম চরিত্রের হাদিস বাংলা","কোমল আচরণের ফজিলত","আখলাক সম্পর্কিত হাদিস"],"related_hadiths":["জামে' আত-তিরমিজি ২৪৮৮","সুনানে ইবনে মাজাহ ৩৬৮৮ (প্রাসঙ্গিক বর্ণনা)","সহিহ বুখারী ৬০২৩ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>{"id":"42","meta_data":{"title":"$book_name$ - 42 ($publication$) | মানুষের মাঝে সমঝোতা করানো সাদাকা","description":"$book_name$ 42 - $chapter_name$. মানুষের মধ্যে সমঝোতা করানো এমন সাদাকা, যা আল্লাহ পছন্দ করেন এবং সমাজে শান্তি ফিরিয়ে আনতে সাহায্য করে।"},"content":{"heading":"মানুষের মাঝে সমঝোতা করানো: আল্লাহর পছন্দের সাদাকা","explanation":"এই হাদিসে মানুষের মাঝে সমঝোতা বা সন্ধি স্থাপনের গুরুত্ব বলা হয়েছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম এটিকে এমন এক সাদাকা বলেছেন, যার পাত্রকে আল্লাহ ভালোবাসেন। এখানে সাদাকা শুধু অর্থ দান নয়; বরং মানুষের ভাঙা সম্পর্ক জোড়া লাগানো, ঝগড়া কমানো এবং ভালো কথার মাধ্যমে শান্তি আনার কাজও সাদাকার মতো মূল্যবান। সমাজে অনেক সময় ভুল বোঝাবুঝি, রাগ বা কথা-কাটাকাটি হয়। এমন সময়ে কেউ যদি ন্যায় ও ভালো উদ্দেশ্যে দুই পক্ষকে কাছাকাছি আনে, তা বড় কল্যাণের কাজ। এই হাদিস আমাদের শেখায়, সম্পর্ক নষ্ট করা নয়, সম্পর্ক ঠিক করা মুমিনের সুন্দর দায়িত্ব।","teachings":["মানুষের ঝগড়া মিটিয়ে দেওয়া সাদাকার মতো কল্যাণকর কাজ।","সমঝোতা করানোর কাজ আল্লাহর পছন্দের আমল হতে পারে।","ভালো কথা ও ন্যায়ভিত্তিক মধ্যস্থতা সমাজে শান্তি আনে।","সম্পর্ক ভাঙার বদলে সম্পর্ক ঠিক করার চেষ্টা করা উচিত।"]},"searching_terms":["সমঝোতা করানো সাদাকা হাদিস","মানুষের মাঝে সন্ধি স্থাপন","বিবাদ মীমাংসার হাদিস","সম্পর্ক ঠিক করার হাদিস","সাদাকা শুধু টাকা নয়","ইসলামে মীমাংসার গুরুত্ব"],"related_hadiths":["সহিহ বুখারী ২৬৯২","সুনানে আবূ দাউদ ৪৯২১ (প্রাসঙ্গিক বর্ণনা)","রিয়াদুস সলেহিন ২৪৯ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>{"id":"43","meta_data":{"title":"$book_name$ - 43 ($publication$) | ক্রোধ নিয়ন্ত্রণই প্রকৃত বীরত্ব","description":"$book_name$ 43 - $chapter_name$. কুস্তি বা শক্তি নয়, রাগের সময় নিজেকে নিয়ন্ত্রণ করাই প্রকৃত বীরত্ব—এ হাদিসে সেই বড় শিক্ষা দেওয়া হয়েছে।"},"content":{"heading":"ক্রোধ নিয়ন্ত্রণের হাদিস: প্রকৃত শক্তিশালী কে?","explanation":"এই হাদিসে বাহ্যিক শক্তির চেয়ে অন্তরের শক্তিকে বড় করে দেখানো হয়েছে। লোকেরা পাথর বহন বা কুস্তির মাধ্যমে বীরত্ব দেখাচ্ছিল। তখন রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম জানালেন, আসল শক্তিশালী সে, যে ক্রোধের সময় নিজেকে নিয়ন্ত্রণ করতে পারে। অন্য বর্ণনায় এসেছে, কেউ অত্যাচার করলেও যে রাগ দমন করে, সে নিজের শত্রু ও শয়তানের উপর এক ধরনের বিজয় লাভ করে। এখানে মূল কথা হলো, রাগ উঠলে প্রতিশোধ, গালি বা আঘাতের দিকে না গিয়ে নিজেকে সামলানো। এটি দুর্বলতা নয়; বরং বড় আত্মনিয়ন্ত্রণ। দৈনন্দিন জীবনে পরিবার, কাজ, বন্ধুত্ব ও সমাজে এই শিক্ষা খুব প্রয়োজন।","teachings":["রাগের সময় নিজেকে নিয়ন্ত্রণ করা বড় বীরত্বের পরিচয়।","বাহ্যিক শক্তির চেয়ে আত্মনিয়ন্ত্রণ বেশি মূল্যবান।","অন্যায় আচরণের মুখেও রাগ দমন করা নেক চরিত্রের অংশ।","ক্রোধের সময় শয়তানের প্ররোচনা থেকে বাঁচার চেষ্টা করতে হবে।"]},"searching_terms":["ক্রোধ নিয়ন্ত্রণের হাদিস","প্রকৃত বীর কে হাদিস","রাগ দমন করার ফজিলত","শক্তিশালী ব্যক্তি হাদিস","রাগের সময় নিজেকে সামলানো","আত্মনিয়ন্ত্রণ ইসলামে"],"related_hadiths":["সহিহ বুখারী ৬১১৪","আদাবুল মুফরাদ ১৩৩০","সুনানে আবূ দাউদ ৪৭৭৯ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+    <row r="37" ht="46" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>{"id":"44","meta_data":{"title":"$book_name$ - 44 ($publication$) | বিনয়, তাওহিদ ও জান্নাত-জাহান্নামের মানুষের গুণ","description":"$book_name$ 44 - $chapter_name$. হাদিসে তাওহিদ, শয়তানের বিভ্রান্তি, জান্নাতি-জাহান্নামি গুণ এবং বিনয়ী হওয়ার নির্দেশ একসাথে এসেছে।"},"content":{"heading":"বিনয় ও তাওহিদের শিক্ষা: জান্নাতি মানুষের গুণাবলি","explanation":"এই দীর্ঘ হাদিসে কয়েকটি বড় শিক্ষা একসাথে এসেছে। আল্লাহ মানুষকে একশ্বরবাদ বা হিদায়তের উপর সৃষ্টি করেছেন, কিন্তু শয়তান মানুষকে মূল পথ থেকে সরিয়ে দেয় এবং হালালকে হারাম বানানোর মতো বিভ্রান্তিতে ফেলতে চায়। এখানে জান্নাতের বাসিন্দাদের মধ্যে ন্যায়পরায়ণ ক্ষমতাবান, দয়ালু ব্যক্তি, আত্মীয় ও মুসলিমের প্রতি সুহৃদয়বান এবং সচ্চরিত্র মানুষের কথা এসেছে। জাহান্নামের অধিবাসীদের মধ্যে খিয়ানতকারী, ধোঁকাবাজ, কৃপণ বা মিথ্যাবাদী এবং অশ্রাব্যভাষী অসচ্চরিত্র মানুষের কথা বলা হয়েছে। শেষে বড় শিক্ষা হলো বিনয়ী হওয়া, একে অন্যের উপর গর্ব না করা এবং কাউকে জুলুম না করা।","teachings":["তাওহিদ মানুষের মূল হিদায়তের পথ।","ন্যায়, দয়া, দানশীলতা ও সচ্চরিত্র জান্নাতি গুণ হিসেবে এসেছে।","খিয়ানত, ধোঁকা, মিথ্যা, কৃপণতা ও অশ্লীল ভাষা থেকে বাঁচতে হবে।","বিনয়ী থাকা, অহংকার না করা এবং জুলুম না করা জরুরি শিক্ষা।"]},"searching_terms":["জান্নাতের বাসিন্দা তিন প্রকার","জাহান্নামের অধিবাসী পাঁচ প্রকার","বিনয়ী হওয়ার হাদিস","তাওহিদ ও শয়তানের বিভ্রান্তি","খিয়ানত ধোঁকা মিথ্যা হাদিস","উত্তম চরিত্র ও বিনয়"],"related_hadiths":["সহিহ মুসলিম ৭১০২","সুনানে ইবনে মাজাহ ৪২১৪","সহিহ বুখারী ৬১৩৬ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>{"id":"45","meta_data":{"title":"$book_name$ - 45 ($publication$) | চোগলখুরী মানুষের মাঝে বিশৃঙ্খলা সৃষ্টি করে","description":"$book_name$ 45 - $chapter_name$. মানুষের ভালো-মন্দ কথা ছড়ানো ও চোগলখুরী সম্পর্ক নষ্ট করে; হাদিসে এটিকে বিশৃঙ্খলার কারণ বলা হয়েছে।"},"content":{"heading":"চোগলখুরীর হাদিস: কথার মাধ্যমে ফিতনা তৈরি করা","explanation":"এই হাদিসে রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম ‘আল-আজহ’ শব্দের ব্যাখ্যা করেছেন। তিনি বলেছেন, মানুষের ভালো-মন্দ কথা নিয়ে চোগলখুরী করাই এর অর্থ। আরেক বর্ণনায় এসেছে, চোগলখুরী হলো এমন কাজ, যা মানুষের মধ্যে বিশৃঙ্খলা সৃষ্টি করে। এখানে শিক্ষা খুব পরিষ্কার: কথা মানুষের সম্পর্ক গড়তেও পারে, আবার ভাঙতেও পারে। এক জনের কথা অন্য জনের কাছে এমনভাবে বলা, যাতে রাগ, সন্দেহ বা শত্রুতা তৈরি হয়, তা ভয়ংকর আচরণ। মুমিনের মুখ থেকে এমন কথা বের হওয়া উচিত নয়, যা মানুষের মধ্যে ঝগড়া বাড়ায়। বরং কথা বলার আগে তার ফল ভাবা দরকার।","teachings":["চোগলখুরী মানুষের সম্পর্ক নষ্ট করে।","একজনের কথা অন্যজনের কাছে লাগানো থেকে বাঁচতে হবে।","যে কথা বিশৃঙ্খলা তৈরি করে, তা বলা উচিত নয়।","মুমিনের ভাষা শান্তি ও ভালো সম্পর্কের সহায়ক হওয়া উচিত।"]},"searching_terms":["চোগলখুরী হাদিস","মানুষের মাঝে বিশৃঙ্খলা সৃষ্টি","নামিমা সম্পর্কে হাদিস","কথা লাগানো ইসলামে","চোগলখোরের পরিণাম","আখলাক ও জিহ্বা সংযম"],"related_hadiths":["সহিহ বুখারী ৬০৫৬","সহিহ মুসলিম ১০৫","সুনানে আবূ দাউদ ৪৮৭১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
+    <row r="39" ht="46" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>{"id":"46","meta_data":{"title":"$book_name$ - 46 ($publication$) | স্বামী-স্ত্রীর গোপন কথা প্রকাশের নিষেধ","description":"$book_name$ 46 - $chapter_name$. স্বামী-স্ত্রীর একান্ত বিষয় অন্যদের কাছে বলা কঠোরভাবে নিষেধ; হাদিসে এর নিন্দনীয় উদাহরণ দেওয়া হয়েছে।"},"content":{"heading":"স্বামী-স্ত্রীর গোপনীয়তা রক্ষা: একান্ত কথার আমানত","explanation":"এই হাদিসে রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম আনসারী নারীদের উপদেশ দেন, সাদাকা করতে বলেন এবং এরপর খুব গুরুত্বপূর্ণ একটি সতর্কতা জানান। তিনি বলেন, কোনো নারী যেন স্বামীর সাথে একাকী অবস্থার কথা অন্যদের না বলে এবং কোনো পুরুষও যেন স্ত্রীর সাথে একান্তে যা হয়েছে তা মানুষের কাছে প্রকাশ না করে। হাদিসে এমন কাজের জন্য খুব নিন্দনীয় উদাহরণ দেওয়া হয়েছে, যাতে বোঝা যায় বিষয়টি কতটা লজ্জাজনক। স্বামী-স্ত্রীর সম্পর্ক বিশ্বাস ও গোপনীয়তার উপর দাঁড়িয়ে থাকে। তাই একান্ত বিষয় বন্ধু, আত্মীয় বা সমাজের আলোচনার বিষয় বানানো উচিত নয়। এটি আমানত রক্ষার অংশ।","teachings":["স্বামী-স্ত্রীর একান্ত বিষয় গোপন রাখা জরুরি।","দাম্পত্য সম্পর্কের কথা অন্যদের কাছে বলা নিন্দনীয় কাজ।","বিশ্বাস রক্ষা করা সংসারের গুরুত্বপূর্ণ ভিত্তি।","লজ্জা ও শালীনতা মুমিনের চরিত্রের অংশ।"]},"searching_terms":["স্বামী স্ত্রীর গোপন কথা হাদিস","দাম্পত্য গোপনীয়তা ইসলাম","স্ত্রীর কথা প্রকাশ করা নিষেধ","স্বামীর একান্ত কথা বলা","বিবাহিত জীবনের গোপনীয়তা","লজ্জা শালীনতা হাদিস"],"related_hadiths":["সহিহ মুসলিম ১৪৩৭","সুনানে আবূ দাউদ ৪৮৭০","মিশকাতুল মাসাবিহ ৩১৯০ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+    <row r="40" ht="46" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>{"id":"47","meta_data":{"title":"$book_name$ - 47 ($publication$) | আনসার কিশোরীদের প্রতি নবীর ভালোবাসা","description":"$book_name$ 47 - $chapter_name$. বনী নাজ্জারের কিশোরীদের আনন্দঘন কথার জবাবে নবীজি তাদের প্রতি নিজের ভালোবাসা প্রকাশ করেন।"},"content":{"heading":"আনসারদের ভালোবাসা: বনী নাজ্জারের কিশোরীদের ঘটনা","explanation":"এই হাদিসে একটি কোমল ও মানবিক দৃশ্য এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বনী নাজ্জার গোত্রের মহল্লা দিয়ে যাচ্ছিলেন। কিছু কিশোরী দফ বাজাচ্ছিল এবং আনন্দের সাথে বলছিল, আমরা বনী নাজ্জারের কিশোরী, আমাদের প্রতিবেশী মুহাম্মাদ কতই না উত্তম। তখন নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেন, আল্লাহ জানেন, আমার হৃদয় তোমাদের ভালোবাসে। এখানে আনসারদের প্রতি নবীজির ভালোবাসা, শিশু-কিশোরীদের প্রতি স্নেহ এবং সুন্দর কথার সুন্দর জবাব দেখা যায়। হাদিসটি কঠোরতা নয়, বরং ভালোবাসা, সৌজন্য ও কোমল আচরণের শিক্ষা দেয়।","teachings":["শিশু-কিশোরদের প্রতি স্নেহপূর্ণ আচরণ নবীজির চরিত্রে ছিল।","ভালোবাসার কথা সুন্দরভাবে প্রকাশ করা বৈধ ও সুন্দর আচরণ।","আনসারদের প্রতি নবীজির ভালোবাসার দৃষ্টান্ত এখানে এসেছে।","সুন্দর কথা শুনলে ভালো জবাব দেওয়া উত্তম আখলাকের অংশ।"]},"searching_terms":["বনী নাজ্জার কিশোরী হাদিস","আনসারদের প্রতি নবীর ভালোবাসা","দফ বাজানো কিশোরী হাদিস","আমার হৃদয় তোমাদের ভালবাসে হাদিস","নবীজির স্নেহময় আচরণ","আনসারদের ফজিলত হাদিস"],"related_hadiths":["সহিহ বুখারী ৩৭৮৫","সহিহ বুখারী ৩৭৮৬ (প্রাসঙ্গিক বর্ণনা)","জামে' আত-তিরমিজি ৩৯০১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+    <row r="41" ht="46" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>{"id":"48","meta_data":{"title":"$book_name$ - 48 ($publication$) | শিশুকে মিথ্যা প্রতিশ্রুতি না দেওয়ার শিক্ষা","description":"$book_name$ 48 - $chapter_name$. শিশুকে কিছু দেওয়ার কথা বলে না দিলে তা মিথ্যা হিসেবে গণ্য হতে পারে—হাদিসে সত্যবাদিতার এ শিক্ষা এসেছে।"},"content":{"heading":"শিশুর সাথে সত্য বলা: মিথ্যা প্রতিশ্রুতি থেকে সাবধান","explanation":"এই হাদিসে দেখা যায়, এক মা তার ছোট সন্তানকে ডাকলেন এবং বললেন, তাকে কিছু দেবেন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম জিজ্ঞেস করলেন, তিনি কী দিতে চান। মা বললেন, তিনি খেজুর দেবেন। তখন নবীজি জানালেন, যদি কিছু না দিতেন, তবে তার আমলনামায় একটি মিথ্যা লেখা হতো। এই হাদিসের মূল শিক্ষা হলো, শিশুর সাথেও সত্য কথা বলতে হবে। অনেক সময় বড়রা শিশুকে শান্ত করতে বা ডাকতে এমন প্রতিশ্রুতি দেয়, যা রাখার ইচ্ছা থাকে না। হাদিসটি শেখায়, ছোটদের ক্ষেত্রেও কথা আমানত। শিশুর মনে সত্যবাদিতার শিক্ষা দিতে হলে বড়দের কথাও সত্য হতে হবে।","teachings":["শিশুকে মিথ্যা প্রতিশ্রুতি দেওয়া উচিত নয়।","ছোটদের সাথেও সত্য কথা বলা ইসলামের শিক্ষা।","কথা দিলে তা রাখার চেষ্টা করতে হবে।","বড়দের আচরণ থেকেই শিশুরা সত্যবাদিতা শেখে।"]},"searching_terms":["শিশুকে মিথ্যা বলা হাদিস","মিথ্যা প্রতিশ্রুতি হাদিস","বাচ্চাকে কিছু দিব বলা","সত্যবাদিতা শেখানোর হাদিস","শিশুর সাথে সত্য কথা","আমলনামায় মিথ্যা লেখা হাদিস"],"related_hadiths":["সুনানে আবূ দাউদ ৪৯৯১","সহিহ বুখারী ৬০৯৪ (প্রাসঙ্গিক বর্ণনা)","সহিহ মুসলিম ২৬০৭ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+    <row r="42" ht="46" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>{"id":"49","meta_data":{"title":"$book_name$ - 49 ($publication$) | জাহেলী অহংকার দূর ও তাকওয়ার মর্যাদা","description":"$book_name$ 49 - $chapter_name$. মক্কা বিজয়ের দিনে নবীজি জাহেলী গৌরব-অহংকার দূর করে তাকওয়া ও সৎ জীবনের মর্যাদা তুলে ধরেন।"},"content":{"heading":"জাহেলী অহংকার নয়, তাকওয়াই মর্যাদার পথ","explanation":"এই হাদিসে মক্কা বিজয়ের দিনের একটি ভাষণ এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাওয়াফের পর আল্লাহর প্রশংসা করেন এবং মানুষকে জানান যে আল্লাহ জাহেলী যুগের গৌরব-অহংকার দূর করে দিয়েছেন। এরপর তিনি মানুষকে দুই শ্রেণীতে ভাগ করে বলেন: সৎ, পরহেজগার ও আল্লাহর পছন্দনীয়; আর অসৎ, হতভাগ্য ও আল্লাহর অপছন্দনীয়। তিনি কুরআনের আয়াতও তিলাওয়াত করেন, যেখানে মানুষের পুরুষ-নারী হিসেবে সৃষ্টি এবং গোত্রে ভাগ হওয়াকে পরিচয়ের জন্য বলা হয়েছে। এখানে মূল শিক্ষা হলো, বংশ, জাতি বা গোত্র নিয়ে অহংকার নয়; আসল মর্যাদা সৎ জীবন ও তাকওয়ার সাথে জড়িত।","teachings":["জাহেলী গৌরব ও বংশগত অহংকার দূর করা ইসলামের শিক্ষা।","মানুষের মর্যাদা সৎকর্ম ও তাকওয়ার সাথে সম্পর্কিত।","গোত্র ও জাতিগত পরিচয় অহংকারের জন্য নয়, পরিচয়ের জন্য।","মক্কা বিজয়ের ভাষণে নবীজি ক্ষমা ও আল্লাহর দিকে ফিরে যাওয়ার শিক্ষা দেন।"]},"searching_terms":["মক্কা বিজয়ের ভাষণ হাদিস","জাহেলী অহংকার দূর হাদিস","তাকওয়ার মর্যাদা হাদিস","সূরা হুজুরাত ১৩ হাদিস","বংশ নিয়ে অহংকার ইসলাম","মানুষ দুই শ্রেণীর হাদিস"],"related_hadiths":["জামে' আত-তিরমিজি ৩২৭০","সুনানে আবূ দাউদ ৫১১৬ (প্রাসঙ্গিক বর্ণনা)","মিশকাতুল মাসাবিহ ৪৮৯৬ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>{"id":"5","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | চোগলখুরীর ভয়াবহ ক্ষতি","description":"$book_name$ $hadith_number$ - $chapter_name$. বিশৃঙ্খলা সৃষ্টির জন্য একের কথা অন্যের কাছে লাগানোই চোগলখুরী—এ শিক্ষা এসেছে।"},"content":{"heading":"চোগলখুরী কী: মানুষের মাঝে বিশৃঙ্খলা সৃষ্টির সতর্কতা","explanation":"এই হাদিসে রাসুলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম সাহাবীদের জিজ্ঞেস করেন, তোমরা জান চোগলখুরী কী? সাহাবীরা বিনয়ের সঙ্গে বলেন, আল্লাহ ও তাঁর রাসুলই ভালো জানেন। এরপর রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেন, চোগলখুরী হলো বিশৃঙ্খলা সৃষ্টির উদ্দেশ্যে একের কথা অন্যের নিকট লাগানো। এখানে শুধু কথা বলা নয়, কথার উদ্দেশ্যও গুরুত্বপূর্ণ। কেউ যদি মানুষের সম্পর্ক নষ্ট করার জন্য কথা বহন করে, সেটিই চোগলখুরীর অন্তর্ভুক্ত। হাদিসটি হাসান বলা হয়েছে। এই হাদিস চোগলখুরী, গীবত নয় বরং কথার অপব্যবহার এবং সম্পর্ক নষ্ট করার বিষয়ে সতর্ক করে। মুসলিমের মুখ থেকে এমন কথা বের হওয়া উচিত নয়, যা মানুষের মাঝে অশান্তি বাড়ায়।","teachings":["চোগলখুরী হলো বিশৃঙ্খলা সৃষ্টির জন্য একের কথা অন্যের কাছে লাগানো।","কথার পেছনের উদ্দেশ্যও ইসলামে গুরুত্বপূর্ণ।","মানুষের সম্পর্ক নষ্ট করে এমন কথা থেকে দূরে থাকা উচিত।","সাহাবীরা না জানলে আল্লাহ ও রাসুলের জ্ঞানের দিকে বিষয়টি সোপর্দ করতেন।"]},"searching_terms":["চোগলখুরী কী হাদিস","চোগলখুরী নিয়ে হাদিস","একের কথা অন্যের কাছে লাগানো","সিলসিলা সহিহা ৫","ইসলামে চোগলখুরীর শাস্তি","মানুষের মাঝে বিশৃঙ্খলা সৃষ্টি"],"related_hadiths":["সিলসিলা সহিহা ১৪","সিলসিলা সহিহা ৪","সিলসিলা সহিহা ৯ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>{"id":"50","meta_data":{"title":"$book_name$ - 50 ($publication$) | শহীদের সন্তানের প্রতি নবীজির স্নেহ","description":"$book_name$ 50 - $chapter_name$. পিতা শহীদ হওয়ায় কাঁদতে থাকা শিশুকে নবীজি সান্ত্বনা দেন এবং নিজের স্নেহময় আশ্রয়ের কথা বলেন।"},"content":{"heading":"শোকের সময় সান্ত্বনা: শহীদের সন্তানের প্রতি নবীজির দয়া","explanation":"এই হাদিসে রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামের দয়া ও স্নেহের একটি সুন্দর ছবি দেখা যায়। বর্ণনাকারীর বাবা এক যুদ্ধে শহীদ হন। তিনি তখন কাঁদছিলেন। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তার পাশ দিয়ে গিয়ে তাকে শান্ত হতে বলেন এবং স্নেহভরা ভাষায় বলেন, সে কি খুশি হবে না যদি তিনি তার পিতা হন এবং আয়েশা রাদিয়াল্লাহু আনহা তার মা হন। এখানে কোনো দীর্ঘ আলোচনা নেই, কিন্তু একটি ব্যথিত শিশুকে সান্ত্বনা দেওয়ার গভীর শিক্ষা আছে। দুঃখের সময়ে কোমল কথা, কাছে দাঁড়ানো এবং হৃদয় দিয়ে সহানুভূতি দেখানো মুমিনের সুন্দর আচরণ।","teachings":["শোকাহত শিশুকে স্নেহ ও কোমল কথায় সান্ত্বনা দেওয়া উচিত।","নবীজি দুঃখে থাকা মানুষের পাশে দাঁড়াতেন।","শহীদের পরিবারের প্রতি দয়া ও যত্ন দেখানো গুরুত্বপূর্ণ।","কান্না দেখলে কঠোরতা নয়, সহানুভূতি দেখানো উত্তম।"]},"searching_terms":["শহীদের সন্তানকে সান্ত্বনা হাদিস","নবীজির দয়া হাদিস","শোকের সময় সান্ত্বনা ইসলাম","আমি তোমার পিতা আয়েশা তোমার মা হাদিস","এতিম শিশুর প্রতি স্নেহ","রাসূলের কোমল আচরণ"],"related_hadiths":["সহিহ বুখারী ৬০০৫","সহিহ বুখারী ৫৯৯৫ (প্রাসঙ্গিক বর্ণনা)","জামে' আত-তিরমিজি ১৯১৮ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+    <row r="45" ht="46" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>{"id":"51","meta_data":{"title":"$book_name$ - 51 ($publication$) | বন্দির ঘটনায় দয়া দেখানোর শিক্ষা","description":"$book_name$ 51 - $chapter_name$. এক বন্দি ও নারীর করুণ ঘটনায় নবীজি প্রশ্ন করেন—তোমাদের মধ্যে কি কোনো দয়ালু ব্যক্তি ছিল না?"},"content":{"heading":"দয়া ও মানবিকতা: কঠিন অবস্থাতেও কোমল হৃদয়ের শিক্ষা","explanation":"এই হাদিসে একটি কঠিন ও বেদনাদায়ক ঘটনা এসেছে। এক সারিয়া গনীমত লাভ করে এবং তাদের মধ্যে এক ব্যক্তি ছিল, যে জানায় সে তাদের সদস্য নয়; সে এক নারীর প্রেমে পড়ে তাকে দেখতে এসেছে। পরে সে নারীকে দেখে কথা বলে। এরপর সৈন্যদল অগ্রসর হয়ে তার গর্দান কেটে ফেলে। নারীটি তার কাছে এসে চিৎকার করে মারা যায়। এই ঘটনা রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামকে জানানো হলে তিনি বলেন, তোমাদের মধ্যে কি কোনো দয়ালু ব্যক্তি ছিল না? হাদিসের মূল শিক্ষা হলো, কঠিন পরিস্থিতিতেও দয়া ও মানবিকতা ভুলে যাওয়া উচিত নয়। সিদ্ধান্তের সময় হৃদয়ের কোমলতা ও বিবেচনা থাকা দরকার।","teachings":["কঠিন অবস্থাতেও দয়া হারিয়ে ফেলা উচিত নয়।","মানুষের বেদনা ও আবেগকে অবহেলা করা ঠিক নয়।","নবীজি দয়ার অভাবকে প্রশ্নের মাধ্যমে বুঝিয়ে দিয়েছেন।","কর্মের আগে তার মানবিক ফল ভাবা দরকার।"]},"searching_terms":["তোমাদের মধ্যে কি কোনো দয়ালু ব্যক্তি ছিল না","দয়া ও মানবিকতা হাদিস","বন্দির ঘটনা হাদিস","সারিয়া ও দয়ার শিক্ষা","রাসূলের দয়া শিক্ষা","ইসলামে কোমল হৃদয়"],"related_hadiths":["সহিহ বুখারী ৬০১৩","সহিহ মুসলিম ২৩১৯ (প্রাসঙ্গিক বর্ণনা)","সুনানে আবূ দাউদ ৪৯৪১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+    <row r="46" ht="46" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>{"id":"52","meta_data":{"title":"$book_name$ - 52 ($publication$) | নবীর চোখের খিয়ানত নেই","description":"$book_name$ 52 - $chapter_name$. বাইআতের ঘটনায় নবীজি স্পষ্ট করেন, কোনো নবীর জন্য চোখের আড়াল ইশারায় খিয়ানত করা সমীচীন নয়।"},"content":{"heading":"চোখের খিয়ানত নয়: নবীর সততা ও পরিষ্কার আচরণ","explanation":"এই হাদিসে মক্কা বিজয়ের দিনের একটি ঘটনা এসেছে। আব্দুল্লাহ ইবনু সা’দ ইবনু আবূ সরাহ উসমান রাদিয়াল্লাহু আনহুর কাছে আশ্রয় নেয়। উসমান রাদিয়াল্লাহু আনহু তাকে নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামের কাছে নিয়ে এসে বাইআতের অনুরোধ করেন। নবীজি কয়েকবার অস্বীকৃতি জানান, পরে বাইআত করান। এরপর সাহাবীদের বলেন, তারা কেন বুঝল না যে তিনি হাত গুটিয়ে নিয়েছিলেন। সাহাবীরা বলেন, তারা মনের কথা জানতেন না; চোখে ইশারা করলে বুঝতেন। তখন নবীজি বলেন, কোনো নবীর জন্য চোখের খিয়ানত থাকা সমীচীন নয়। এখানে সততা, স্পষ্টতা ও গোপন কৌশল থেকে নবীদের পবিত্রতার শিক্ষা আছে।","teachings":["নবীদের আচরণে গোপন খিয়ানত থাকে না।","চোখের ইশারায় প্রতারণামূলক নির্দেশ দেওয়া সমীচীন নয়।","সততা শুধু কথায় নয়, ইশারা-আচরণেও দরকার।","গুরুত্বপূর্ণ বিষয়ে পরিষ্কার ও সৎ অবস্থান রাখা উচিত।"]},"searching_terms":["চোখের খিয়ানত হাদিস","কোনো নবীর জন্য চোখের খিয়ানত নেই","আব্দুল্লাহ ইবনু সাদ আবূ সরাহ","মক্কা বিজয়ের বাইআত ঘটনা","নবীর সততা হাদিস","ইশারায় খিয়ানত ইসলাম"],"related_hadiths":["সুনানে আবূ দাউদ ৪৩৫৯","সুনানে আন-নাসায়ী ৪০৭৮ (প্রাসঙ্গিক বর্ণনা)","মিশকাতুল মাসাবিহ ৩৫৮৪ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+    <row r="47" ht="46" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>{"id":"53","meta_data":{"title":"$book_name$ - 53 ($publication$) | সাতটি নসিহত ও লা হাওলা ওয়ালা কুওয়াতা","description":"$book_name$ 53 - $chapter_name$. দরিদ্রকে ভালোবাসা, সত্য বলা, আত্মীয়তা রাখা ও বেশি লা হাওলা পড়ার সাতটি মূল্যবান নসিহত এসেছে।"},"content":{"heading":"সাতটি নসিহত: সত্য, আত্মীয়তা ও লা হাওলা ওয়ালা কুওয়াতা","explanation":"এই হাদিসে বর্ণনাকারী বলেন, নবী সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাকে সাতটি কাজের আদেশ করেছেন। দরিদ্রদের ভালোবাসা ও তাদের সাথে থাকা, নিজের চেয়ে নিচের অবস্থার মানুষের দিকে তাকানো, আত্মীয়তার সম্পর্ক বজায় রাখা, কারো কাছে কিছু না চাওয়া, তিক্ত হলেও সত্য বলা, আল্লাহর পথে নিন্দুকের নিন্দাকে ভয় না করা এবং বেশি বেশি ‘লা হাওলা ওয়ালা কুওয়াতা ইল্লা বিল্লাহ’ বলা। হাদিসটি ব্যক্তিগত চরিত্র, সামাজিক সম্পর্ক এবং আল্লাহর উপর নির্ভরতার সুন্দর সমন্বয় শেখায়। এখানে অহংকার কমানো, আত্মসম্মান রাখা, সত্যের উপর দাঁড়ানো এবং আল্লাহর সাহায্য স্মরণ করার সহজ পথ দেখানো হয়েছে।","teachings":["দরিদ্রদের ভালোবাসা ও তাদের কাছে থাকা বিনয়ের শিক্ষা দেয়।","তিক্ত হলেও সত্য বলা মুমিনের গুরুত্বপূর্ণ গুণ।","আত্মীয়তা শীতল হলেও সম্পর্ক বজায় রাখার চেষ্টা করতে হবে।","‘লা হাওলা ওয়ালা কুওয়াতা ইল্লা বিল্লাহ’ বেশি বলা উত্তম আমল।"]},"searching_terms":["সাতটি নসিহত হাদিস","লা হাওলা ওয়ালা কুওয়াতা হাদিস","দরিদ্রদের ভালবাসার হাদিস","তিক্ত হলেও সত্য বলা","আত্মীয়তার সম্পর্ক বজায় রাখা","আল্লাহর পথে নিন্দা ভয় না করা"],"related_hadiths":["সহিহ বুখারী ৬৫০২","সহিহ বুখারী ৫৯৮৬ (প্রাসঙ্গিক বর্ণনা)","সহিহ মুসলিম ২৭২০ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>{"id":"54","meta_data":{"title":"$book_name$ - 54 ($publication$) | অধীনস্থদের প্রতি ন্যায় ও দয়ার আচরণ","description":"$book_name$ 54 - $chapter_name$. দাস-দাসীদের ভাই বলা হয়েছে; তাদের নিজের খাবার-পরিধানের মতো দেওয়া ও সাধ্যের বাইরে কাজ না চাপানোর শিক্ষা এসেছে।"},"content":{"heading":"অধীনস্থদের অধিকার: খাবার, পোশাক ও কাজের ভারে ন্যায়","explanation":"এই হাদিসে অধীনস্থ দাস-দাসীদের প্রতি মানবিক ও ন্যায়ভিত্তিক আচরণের শিক্ষা দেওয়া হয়েছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, তারা তোমাদের ভাই; আল্লাহ তাদের তোমাদের অধীন করেছেন। তাই যার অধীনে এমন কেউ থাকবে, তাকে নিজের মতো খাবার ও পোশাক দিতে হবে। তাদের সাধ্যের বাইরে কাজ চাপিয়ে দেওয়া যাবে না। যদি এমন কাজ দেওয়া হয় যা তাদের জন্য কঠিন, তাহলে সাহায্য করতে হবে। হাদিসটির শিক্ষা শুধু দাস-দাসীর প্রসঙ্গে নয়; অধীনস্থ, কর্মচারী বা সাহায্যকারী মানুষের প্রতি ন্যায়, দয়া ও দায়িত্ববোধের দিকও বুঝতে সাহায্য করে। মানুষকে ছোট ভাবা নয়, ভাইয়ের মতো মর্যাদা দেওয়া এখানে মূল কথা।","teachings":["অধীনস্থদের ভাই হিসেবে সম্মান করা উচিত।","নিজে যা খায় ও পরে, তাদের প্রতিও ন্যায্য আচরণ করা দরকার।","সাধ্যের বাইরে কাজ চাপিয়ে দেওয়া নিষেধ।","কঠিন কাজে অধীনস্থদের সাহায্য করা উত্তম আচরণ।"]},"searching_terms":["দাস দাসী তোমাদের ভাই হাদিস","অধীনস্থদের অধিকার ইসলাম","কর্মচারীর সাথে আচরণ হাদিস","নিজে যা খাবে তাকে তাই খাওয়াবে","সাধ্যের বাইরে কাজ চাপানো নিষেধ","ইসলামে শ্রমিকের অধিকার"],"related_hadiths":["সহিহ বুখারী ৩০","সহিহ বুখারী ২৫৪৫","সহিহ মুসলিম ১৬৬১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+    <row r="49" ht="46" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>{"id":"55","meta_data":{"title":"$book_name$ - 55 ($publication$) | উত্তম চরিত্র পরিপূর্ণ ঈমানের পরিচয়","description":"$book_name$ 55 - $chapter_name$. মুমিনদের মধ্যে পরিপূর্ণ ঈমানদার সে, যার চরিত্র উত্তম; উত্তম চরিত্র সালাত-সাওমের মর্যাদায় পৌঁছাতে পারে।"},"content":{"heading":"উত্তম চরিত্রের মর্যাদা: পরিপূর্ণ ঈমানের লক্ষণ","explanation":"এই হাদিসে ঈমান ও চরিত্রের গভীর সম্পর্ক তুলে ধরা হয়েছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, মুমিনদের মধ্যে পরিপূর্ণ ঈমানদার সেই ব্যক্তি, যার চরিত্র সবচেয়ে উত্তম। আরও বলা হয়েছে, উত্তম চরিত্র সালাত ও সাওমের মর্যাদায় পৌঁছে যায়। এখানে সালাত ও সাওমের গুরুত্ব কমানো হয়নি; বরং বোঝানো হয়েছে যে ভালো আচরণ, কোমল ভাষা, ন্যায়, দয়া ও মানুষের সাথে সুন্দর ব্যবহার ঈমানের খুব বড় অংশ। অনেক মানুষ ইবাদত করে, কিন্তু মানুষের সাথে আচরণে কঠোর হয়। এই হাদিস মনে করিয়ে দেয়, ইবাদতের সাথে চরিত্রও সুন্দর হওয়া দরকার। উত্তম চরিত্র ঘর, সমাজ ও নিজের অন্তরকে সুন্দর করে।","teachings":["পরিপূর্ণ ঈমানের সাথে উত্তম চরিত্র গভীরভাবে জড়িত।","ভালো আচরণ আল্লাহর কাছে মূল্যবান আমল হতে পারে।","ইবাদতের পাশাপাশি মানুষের সাথে ব্যবহার সুন্দর করা দরকার।","মুমিনের পরিচয় শুধু কথায় নয়, চরিত্রেও প্রকাশ পায়।"]},"searching_terms":["উত্তম চরিত্রের হাদিস","পরিপূর্ণ ঈমানদার কে","চরিত্র সালাত সাওমের মর্যাদা","ঈমান ও আখলাক হাদিস","ভালো আচরণের ফজিলত","মুমিনের চরিত্র"],"related_hadiths":["জামে' আত-তিরমিজি ১১৬২","সুনানে আবূ দাউদ ৪৬৮২","আদাবুল মুফরাদ ২৭১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+    <row r="50" ht="46" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>{"id":"56","meta_data":{"title":"$book_name$ - 56 ($publication$) | নম্রতা, অহংকার বর্জন ও জুলুম থেকে বাঁচা","description":"$book_name$ 56 - $chapter_name$. আল্লাহর ওহীর শিক্ষা হলো নম্রতা অবলম্বন করা, একে অন্যের উপর গর্ব না করা এবং জুলুম থেকে দূরে থাকা।"},"content":{"heading":"নম্রতা অবলম্বন: অহংকার ও জুলুম থেকে দূরে থাকার হাদিস","explanation":"এই হাদিসে আল্লাহর পক্ষ থেকে একটি সহজ কিন্তু গভীর নির্দেশ এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম জানান, আল্লাহ তাঁর কাছে ওহী করেছেন যে, মানুষ যেন নম্রতা অবলম্বন করে। কেউ যেন অন্যের উপর গর্ব-অহংকার না করে এবং কেউ যেন কারো প্রতি জুলুম না করে। হাদিসটি সামাজিক জীবনের জন্য খুব গুরুত্বপূর্ণ। অহংকার মানুষকে অন্যকে ছোট ভাবতে শেখায়, আর জুলুম মানুষের অধিকার নষ্ট করে। নম্রতা মানুষকে নিজের সীমা বুঝতে সাহায্য করে এবং অন্যকে সম্মান করতে শেখায়। পরিবার, কাজ, সমাজ বা নেতৃত্ব—সব জায়গায় এই শিক্ষা দরকার। মুমিনের আচরণে বিনয়, ন্যায় ও দয়া থাকা উচিত।","teachings":["নম্রতা আল্লাহর নির্দেশিত সুন্দর গুণ।","অন্যের উপর গর্ব করা থেকে বাঁচতে হবে।","কাউকে জুলুম করা বা অধিকার নষ্ট করা নিষেধ।","বিনয়ী আচরণ সমাজে শান্তি ও সম্মান বাড়ায়।"]},"searching_terms":["নম্রতা অবলম্বন হাদিস","অহংকার না করার হাদিস","জুলুম না করার হাদিস","বিনয়ী হওয়ার শিক্ষা","তোমরা নম্রতা অবলম্বন কর","ইসলামে বিনয় ও ন্যায়"],"related_hadiths":["সহিহ মুসলিম ৭১০২","সুনানে ইবনে মাজাহ ৪২১৪","আদাবুল মুফরাদ ৫৪৫ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+    <row r="51" ht="46" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>{"id":"57","meta_data":{"title":"$book_name$ - 57 ($publication$) | দয়া ও উন্নত চরিত্র আল্লাহর পছন্দ","description":"$book_name$ 57 - $chapter_name$. আল্লাহ দয়ালু; তিনি দয়ালু ও উন্নত চরিত্রবানকে ভালোবাসেন এবং অনর্থক বাচালতাকে অপছন্দ করেন।"},"content":{"heading":"দয়ালু চরিত্রের ফজিলত: বাচালতা থেকে সাবধান","explanation":"এই হাদিসে আল্লাহর একটি সুন্দর গুণ এবং মানুষের পছন্দনীয় চরিত্রের কথা এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, আল্লাহ দয়ালু। তিনি দয়ালু ও উন্নত চরিত্রবান মানুষকে ভালোবাসেন। একই সাথে তিনি অনর্থক উক্তিকারী বা বাচাল মানুষকে অপছন্দ করেন। এর অর্থ, কথায় ও কাজে দয়া থাকা দরকার, আর অযথা কথা বলে মানুষের মন কষ্ট দেওয়া বা নিজের চরিত্র নষ্ট করা উচিত নয়। উন্নত চরিত্র মানে শুধু হাসিমুখ নয়; বরং দয়া, সংযম, পরিমিত কথা এবং মানুষের সাথে সুন্দর আচরণ। এই হাদিস আমাদের কথা বলার আগে ভাবতে শেখায়—কথাটি দরকারি কি না, এতে কারও কষ্ট হবে কি না।","teachings":["আল্লাহ দয়ালু এবং দয়ালু চরিত্র পছন্দ করেন।","উন্নত চরিত্রবান হওয়া মুমিনের গুরুত্বপূর্ণ গুণ।","অনর্থক কথা ও বাচালতা থেকে বাঁচতে হবে।","কথা ও আচরণে দয়া রাখা উচিত।"]},"searching_terms":["আল্লাহ দয়ালু হাদিস","দয়ালু চরিত্র হাদিস","উন্নত চরিত্রবান ব্যক্তিকে আল্লাহ ভালবাসেন","বাচালতা অপছন্দ হাদিস","অনর্থক কথা বলা ইসলাম","দয়া ও আখলাক"],"related_hadiths":["সহিহ বুখারী ৬৯২৭","সহিহ মুসলিম ২৫৯৩","জামে' আত-তিরমিজি ২০১৮ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+    <row r="52" ht="46" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>{"id":"58","meta_data":{"title":"$book_name$ - 58 ($publication$) | আত্মীয়তার সম্পর্ক রক্ষার গুরুত্ব","description":"$book_name$ 58 - $chapter_name$. দয়া ও আত্মীয়তার সম্পর্ক রক্ষা করলে আল্লাহ সম্পর্ক রাখেন; সম্পর্ক ছিন্নকারীর জন্য কঠোর সতর্কতা এসেছে।"},"content":{"heading":"আত্মীয়তার সম্পর্ক রক্ষা: দয়ার সাথে আল্লাহর সম্পর্কের শিক্ষা","explanation":"এই হাদিসে দয়া এবং আত্মীয়তার সম্পর্কের মর্যাদা তুলে ধরা হয়েছে। আল্লাহ সৃষ্টি জগত সৃষ্টি করার পর দয়া আল্লাহর কাছে আশ্রয় চায় বিচ্ছিন্নতা থেকে। আল্লাহ বলেন, যে দয়ার সাথে সম্পর্ক রাখবে, তিনি তার সাথে সম্পর্ক রাখবেন; আর যে দয়ার সম্পর্ক ছিন্ন করবে, তিনি তার থেকে সম্পর্ক ছিন্ন করবেন। এরপর রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম কুরআনের আয়াতের দিকে ইঙ্গিত করেন, যেখানে পৃথিবীতে বিপর্যয় সৃষ্টি ও আত্মীয়তার সম্পর্ক ছিন্ন করার নিন্দা আছে। এই হাদিসের শিক্ষা হলো, আত্মীয়তা শুধু সামাজিক রীতি নয়; বরং ঈমানি দায়িত্বের অংশ। রাগ, অভিমান বা দূরত্ব থাকলেও সম্পর্ক ভাঙা থেকে বাঁচার চেষ্টা করা দরকার।","teachings":["আত্মীয়তার সম্পর্ক রক্ষা করা বড় গুরুত্বপূর্ণ আমল।","সম্পর্ক ছিন্ন করা কঠোরভাবে নিন্দিত হয়েছে।","দয়া ও আত্মীয়তা মানুষের চরিত্রকে কোমল করে।","বিপর্যয় সৃষ্টি ও সম্পর্ক ভাঙা থেকে দূরে থাকা উচিত।"]},"searching_terms":["আত্মীয়তার সম্পর্ক রক্ষা হাদিস","রহম সম্পর্ক হাদিস","সম্পর্ক ছিন্ন করার শাস্তি","সিলাতুর রাহিম বাংলা","দয়া ও আত্মীয়তা হাদিস","আত্মীয়তার সম্পর্ক ছিন্ন করা"],"related_hadiths":["সহিহ বুখারী ৫৯৮৭","সহিহ মুসলিম ২৫৫৪","আদাবুল মুফরাদ ৫৩ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+    <row r="53" ht="46" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>{"id":"59","meta_data":{"title":"$book_name$ - 59 ($publication$) | তাওহিদের সাক্ষ্য ও আল্লাহর ক্ষমা","description":"$book_name$ 59 - $chapter_name$. এক ব্যক্তির মিথ্যার ঘটনা সত্ত্বেও তাওহিদের সত্য সাক্ষ্যের কারণে আল্লাহর ক্ষমার কথা হাদিসে এসেছে।"},"content":{"heading":"তাওহিদের সাক্ষ্য: মিথ্যা থেকে সতর্ক ও আল্লাহর দয়ার আশা","explanation":"এই হাদিসে এক ব্যক্তির ঘটনা এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম তাকে একটি কাজ সম্পর্কে জিজ্ঞেস করেন। সে অস্বীকার করে এবং শপথ করে বলে, সেই সত্তার শপথ যিনি ছাড়া কোনো উপাস্য নেই। নবীজি জানতেন, সে কাজটি করেছে। এরপর বলা হয়, আল্লাহ তার মিথ্যা ক্ষমা করে দিয়েছেন, কারণ সে ‘যিনি ছাড়া কোনো উপাস্য নেই’—এই সত্য কথাকে সত্য প্রতিপন্ন করেছে। হাদিসটি মিথ্যা বলাকে হালকা করে না; বরং তাওহিদের বাক্যের মর্যাদা দেখায়। একই সাথে এটি মনে করিয়ে দেয়, মিথ্যা থেকে বাঁচা জরুরি, আর আল্লাহর দয়া বিশাল। তাওহিদের সাক্ষ্য সত্য ও আন্তরিকতার সাথে বলা মুমিনের মূল পরিচয়।","teachings":["মিথ্যা বলা থেকে সতর্ক থাকা দরকার।","তাওহিদের সত্য সাক্ষ্যের বড় মর্যাদা আছে।","আল্লাহর দয়া ও ক্ষমার আশা রাখা যায়।","শপথ ও কথায় সত্যবাদিতা বজায় রাখা উচিত।"]},"searching_terms":["তাওহিদের সাক্ষ্য হাদিস","আল্লাহ তোমার মিথ্যা ক্ষমা করেছেন হাদিস","লা ইলাহা ইল্লাল্লাহ ফজিলত","মিথ্যা ও তাওহিদ হাদিস","শপথ করে মিথ্যা বলা","আল্লাহর ক্ষমা হাদিস"],"related_hadiths":["সহিহ বুখারী ১২৮","সহিহ মুসলিম ১৫৪ (প্রাসঙ্গিক বর্ণনা)","জামে' আত-তিরমিজি ২৬৩৯ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+    <row r="54" ht="46" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>{"id":"6","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | জান্নাতে প্রবেশের পথনির্দেশ","description":"$book_name$ $hadith_number$ - $chapter_name$. ইবাদত, সালাত, যাকাত, রোজা, হজ্জ-উমরাহ ও মানুষের সাথে ভালো আচরণের শিক্ষা এতে এসেছে।"},"content":{"heading":"জান্নাতে প্রবেশের আমল: ইবাদত ও মানুষের সাথে সুন্দর আচরণ","explanation":"এই হাদিসে একজন ব্যক্তি রাসুলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামকে এমন বিষয়ের কথা জিজ্ঞেস করেন, যা তাকে আল্লাহর আযাব থেকে দূরে রাখবে এবং জান্নাতে প্রবেশ করাবে। উত্তরে রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম কয়েকটি মূল আমল বলেন। আল্লাহর ইবাদত করতে হবে এবং তাঁর সঙ্গে কাউকে শরীক করা যাবে না। ফরজ সালাত আদায় করতে হবে, ফরজ যাকাত দিতে হবে, রামাযানের রোজা রাখতে হবে, হজ্জ ও উমরাহ পালন করতে হবে। এরপর মানুষের সাথে এমন আচরণ করতে বলা হয়েছে, যেমন আচরণ নিজের জন্য পছন্দ করা হয়। আবার যে আচরণ নিজের জন্য অপছন্দ, তা অন্যের সাথেও না করতে বলা হয়েছে। হাদিসটি সহীহ বলা হয়েছে। এখানে ইবাদত ও উত্তম আচরণ—দুই দিকই একসাথে এসেছে।","teachings":["আল্লাহর ইবাদত করতে হবে এবং শিরক থেকে দূরে থাকতে হবে।","ফরজ সালাত, যাকাত ও রামাযানের রোজা গুরুত্বপূর্ণ আমল।","হজ্জ ও উমরাহর কথাও এই বর্ণনায় এসেছে।","মানুষের সাথে এমন আচরণ করা উচিত, যা নিজের জন্য পছন্দ করা হয়।"]},"searching_terms":["জান্নাতে প্রবেশের আমল","আল্লাহর আযাব থেকে মুক্তির আমল","ফরজ সালাত যাকাত রোজা হাদিস","মানুষের সাথে ভালো আচরণ হাদিস","সিলসিলা সহিহা ৬","ইবাদত ও উত্তম আচরণ"],"related_hadiths":["সিলসিলা সহিহা ৯","সিলসিলা সহিহা ১৩","সিলসিলা সহিহা ৮ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+    <row r="55" ht="46" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>{"id":"60","meta_data":{"title":"$book_name$ - 60 ($publication$) | উত্তম চরিত্র, রিজিক ও জিকিরের শিক্ষা","description":"$book_name$ 60 - $chapter_name$. আল্লাহ যেমন রিজিক দেন, তেমনি চরিত্র বণ্টন করেন; ভয় ও কৃপণতা কাটাতে বেশি জিকিরের শিক্ষা এসেছে।"},"content":{"heading":"উত্তম চরিত্র ও জিকির: রিজিক, ঈমান ও আল্লাহর দানের শিক্ষা","explanation":"এই হাদিসে চরিত্র, রিজিক, ঈমান এবং জিকিরের সম্পর্ক নিয়ে গভীর শিক্ষা এসেছে। রাসূলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম বলেছেন, আল্লাহ মানুষের মাঝে উত্তম চরিত্র বণ্টন করেন, যেমন তিনি রিজিক বণ্টন করেন। দুনিয়ার সম্পদ তিনি যাকে ভালোবাসেন তাকেও দেন, যাকে অপছন্দ করেন তাকেও দেন। কিন্তু ঈমান দেন সেই ব্যক্তিকে, যাকে তিনি ভালোবাসেন। এরপর বলা হয়েছে, যে ব্যক্তি সম্পদ খরচ হওয়ার ভয়ে কৃপণতা করে, শত্রুর বিরুদ্ধে লড়তে ভয় পায় বা রাতে সফরে আশংকা করে, সে যেন বেশি বেশি ‘সুবহানআল্লাহ’, ‘আলহামদুলিল্লাহ’, ‘লা ইলাহা ইল্লাল্লাহ’ এবং ‘আল্লাহু আকবার’ পড়ে। হাদিসটি দুনিয়া, ঈমান ও আল্লাহর স্মরণের ভারসাম্য শেখায়।","teachings":["উত্তম চরিত্র আল্লাহর বড় দান।","দুনিয়ার সম্পদ ভালোবাসার একমাত্র চিহ্ন নয়।","ঈমান আল্লাহর বিশেষ অনুগ্রহের বিষয়।","ভয় ও কৃপণতার সময় বেশি বেশি তাসবিহ, তাহমিদ, তাহলিল ও তাকবির পড়া উচিত।"]},"searching_terms":["উত্তম চরিত্র বণ্টন হাদিস","রিজিক ও চরিত্র হাদিস","ঈমান আল্লাহ যাকে ভালোবাসেন","সুবহানআল্লাহ আলহামদুলিল্লাহ লা ইলাহা ইল্লাল্লাহ","কৃপণতা ভয় দূর করার জিকির","তাসবিহ তাহমিদ তাহলিল তাকবির"],"related_hadiths":["আদাবুল মুফরাদ ২৭৫","সহিহ মুসলিম ২১৩৭ (প্রাসঙ্গিক বর্ণনা)","সুনানে ইবনে মাজাহ ৩৮১১ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+    <row r="56" ht="46" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>{"id":"7","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | তাকওয়া ও মর্যাদার আসল মানদণ্ড","description":"$book_name$ $hadith_number$ - $chapter_name$. সর্বোত্তম মানুষ সম্পর্কে প্রশ্নের জবাবে তাকওয়া, নবী ইউসুফ ও ইলম-আমলের মর্যাদা শেখানো হয়েছে।"},"content":{"heading":"সর্বোত্তম মানুষ কে: তাকওয়া ও ইলম-আমলের শিক্ষা","explanation":"এই হাদিসে রাসুলুল্লাহ সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লামকে জিজ্ঞেস করা হলো, সর্বোত্তম মানুষ কে? তিনি প্রথমে বলেন, যে সর্বাধিক আল্লাহভীরু, সেই সর্বোত্তম। সাহাবীরা জানান, তারা এ বিষয়ে জানতে চাননি। এরপর তিনি ইউসুফ আলাইহিস সালামের কথা বলেন, যিনি নিজে নাবী, নাবীর পুত্র, নাবীর পৌত্র এবং খলিলুল্লাহ ইব্রাহীম আলাইহিস সালামের বংশধর। সাহাবীরা আবার বলেন, তারা এ বিষয়েও জানতে চাননি। তখন তিনি আরবের সম্ভ্রান্তদের প্রসঙ্গে বলেন, জাহেলী যুগের সম্ভ্রান্তরা ইসলামী যুগেও সম্ভ্রান্ত, যদি তারা বিদ্যায় অগ্রগামী হয়। হাদিসটি সহীহ বলা হয়েছে। এই হাদিসে তাকওয়া, বংশের মর্যাদা এবং ইলম-আমলের গুরুত্ব একসাথে এসেছে।","teachings":["সর্বোত্তম হওয়ার আসল মানদণ্ড হলো আল্লাহভীতি।","ইউসুফ আলাইহিস সালামের মর্যাদা বিশেষভাবে উল্লেখ করা হয়েছে।","বংশের মর্যাদা থাকলেও ইলম ও আমল ছাড়া তা পূর্ণ হয় না।","প্রশ্নের ধরন অনুযায়ী রাসুল সাল্লাল্লাহু ‘আলাইহি ওয়াসাল্লাম ভিন্ন দিক থেকে উত্তর দিয়েছেন।"]},"searching_terms":["সর্বোত্তম মানুষ কে হাদিস","তাকওয়া নিয়ে হাদিস","ইউসুফ আলাইহিস সালাম মর্যাদা","ইলম ও আমলের গুরুত্ব","সিলসিলা সহিহা ৭","আল্লাহভীরু মানুষ হাদিস"],"related_hadiths":["সিলসিলা সহিহা ৯","সিলসিলা সহিহা ১৩","সিলসিলা সহিহা ১২ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>bn</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
+    <row r="57" ht="46" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>{"id":"9","meta_data":{"title":"$book_name$ - $hadith_number$ ($publication$) | মিযানে উত্তম চরিত্রের ওজন","description":"$book_name$ $hadith_number$ - $chapter_name$. কিয়ামতের মিযানে উত্তম চরিত্র ভারী বস্তু—এই হাদিসে সুন্দর চরিত্রের মূল্য শেখানো হয়েছে।"},"content":{"heading":"উত্তম চরিত্র: কিয়ামতের মিযানে ভারী আমল","explanation":"এই হাদিসে আবূ দারদা রাঃ থেকে বর্ণিত হয়েছে যে, কিয়ামাতের দিনে পাপ-পুণ্য মাপার পাল্লায় সবচেয়ে ভারী বস্তু হলো উত্তম চরিত্র। হাদিসটি সহীহ বলা হয়েছে। এখানে উত্তম চরিত্রের গুরুত্ব খুব স্পষ্টভাবে এসেছে। মানুষ অনেক আমলের কথা জানে, কিন্তু আচরণ, কথা, রাগ নিয়ন্ত্রণ, মানুষের প্রতি নরম ব্যবহার—এসবও চরিত্রের অংশ। এই হাদিস আমাদের শেখায়, ভালো চরিত্র শুধু সামাজিক সৌন্দর্য নয়; আখিরাতের হিসাবেও এর মূল্য আছে। তাই মিযানে উত্তম চরিত্র, ভালো ব্যবহার এবং নৈতিক জীবন—এই বিষয়গুলো একজন মুসলিমের কাছে গুরুত্বপূর্ণ হওয়া উচিত। হাদিসের ভাষা সংক্ষিপ্ত, কিন্তু তা চরিত্র গঠনের জন্য শক্ত প্রেরণা দেয়।","teachings":["কিয়ামতের মিযানে উত্তম চরিত্রের বড় মূল্য আছে।","ভালো ব্যবহার ইসলামী জীবনের গুরুত্বপূর্ণ অংশ।","চরিত্র শুধু মানুষের সাথে সম্পর্ক নয়, আখিরাতের হিসাবের সাথেও যুক্ত।","মুমিনের উচিত নিজের কথা ও আচরণ সুন্দর করা।"]},"searching_terms":["মিযানে উত্তম চরিত্র হাদিস","উত্তম চরিত্রের গুরুত্ব","সিলসিলা সহিহা ৯","কিয়ামতের পাল্লায় ভারী আমল","ভালো চরিত্র হাদিস","আখিরাতে চরিত্রের মূল্য"],"related_hadiths":["সিলসিলা সহিহা ১২","সিলসিলা সহিহা ১৩","সিলসিলা সহিহা ১০ (প্রাসঙ্গিক বর্ণনা)"]}</t>
         </is>

--- a/SINGLE HADITH CONTENT/BOOK WISE FINAL/BN/BN_SILSILA SAHIHA.xlsx
+++ b/SINGLE HADITH CONTENT/BOOK WISE FINAL/BN/BN_SILSILA SAHIHA.xlsx
@@ -60,8 +60,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
